--- a/database/event/2100/event_2100_evp_summary.xlsx
+++ b/database/event/2100/event_2100_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.4227</v>
+        <v>4.3599</v>
       </c>
       <c r="C2" t="n">
-        <v>2.05</v>
+        <v>2.0209</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3653</v>
+        <v>1.2931</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4227</v>
+        <v>4.3599</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4227</v>
+        <v>4.3599</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6317</v>
+        <v>4.5333</v>
       </c>
       <c r="I2" t="n">
-        <v>4.807</v>
+        <v>4.7273</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.807</v>
+        <v>4.7273</v>
       </c>
       <c r="N2" t="n">
-        <v>249</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.9132</v>
+        <v>4.3415</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8139</v>
+        <v>2.0124</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1595</v>
+        <v>1.2857</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9132</v>
+        <v>4.3415</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9132</v>
+        <v>4.3415</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9132</v>
+        <v>4.5044</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0051</v>
+        <v>4.8167</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.0051</v>
+        <v>4.8167</v>
       </c>
       <c r="N3" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4">
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3786</v>
+        <v>4.1184</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5661</v>
+        <v>1.909</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9435</v>
+        <v>1.1969</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3786</v>
+        <v>4.1184</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3786</v>
+        <v>4.1184</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3786</v>
+        <v>4.1545</v>
       </c>
       <c r="I4" t="n">
-        <v>3.458</v>
+        <v>4.3323</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.458</v>
+        <v>4.3323</v>
       </c>
       <c r="N4" t="n">
         <v>222</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.302</v>
+        <v>3.7849</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5306</v>
+        <v>1.7544</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9126</v>
+        <v>1.064</v>
       </c>
       <c r="E5" t="n">
-        <v>3.302</v>
+        <v>3.7849</v>
       </c>
       <c r="F5" t="n">
-        <v>3.302</v>
+        <v>3.7849</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.302</v>
+        <v>3.7849</v>
       </c>
       <c r="I5" t="n">
-        <v>3.427</v>
+        <v>4.0474</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.427</v>
+        <v>4.0474</v>
       </c>
       <c r="N5" t="n">
         <v>249</v>
@@ -676,553 +676,553 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4149</v>
+        <v>3.5248</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1194</v>
+        <v>1.6338</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5542</v>
+        <v>0.9604</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4149</v>
+        <v>3.5248</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4149</v>
+        <v>3.5248</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4149</v>
+        <v>3.5248</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5063</v>
+        <v>3.6146</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5063</v>
+        <v>3.6146</v>
       </c>
       <c r="N6" t="n">
-        <v>249</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.2096</v>
+        <v>2.9376</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0242</v>
+        <v>1.3617</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4713</v>
+        <v>0.7264</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2096</v>
+        <v>2.9376</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2096</v>
+        <v>2.9376</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2096</v>
+        <v>2.9376</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2406</v>
+        <v>3.1413</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2406</v>
+        <v>3.1413</v>
       </c>
       <c r="N7" t="n">
-        <v>165</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6648</v>
+        <v>2.4584</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7717000000000001</v>
+        <v>1.1395</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2512</v>
+        <v>0.5355</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6648</v>
+        <v>2.4584</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6648</v>
+        <v>2.4584</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6648</v>
+        <v>2.4584</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7278</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7278</v>
+        <v>2.5</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5219</v>
+        <v>2.3438</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7054</v>
+        <v>1.0864</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1935</v>
+        <v>0.4899</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5219</v>
+        <v>2.3438</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5219</v>
+        <v>2.3438</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5219</v>
+        <v>2.3438</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5433</v>
+        <v>2.5063</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>156</v>
+        <v>249</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5433</v>
+        <v>2.5063</v>
       </c>
       <c r="N9" t="n">
-        <v>156</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3304</v>
+        <v>2.097</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6167</v>
+        <v>0.972</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1161</v>
+        <v>0.3915</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3304</v>
+        <v>2.097</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3304</v>
+        <v>2.097</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3304</v>
+        <v>2.097</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3429</v>
+        <v>2.1146</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3429</v>
+        <v>2.1146</v>
       </c>
       <c r="N10" t="n">
-        <v>123</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1784</v>
+        <v>2.0585</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5462</v>
+        <v>0.9542</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0547</v>
+        <v>0.3762</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1784</v>
+        <v>2.0585</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1784</v>
+        <v>2.0585</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1784</v>
+        <v>2.0585</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1839</v>
+        <v>2.1109</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1839</v>
+        <v>2.1109</v>
       </c>
       <c r="N11" t="n">
-        <v>87</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.1422</v>
+        <v>1.9387</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5294</v>
+        <v>0.8986</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0401</v>
+        <v>0.3285</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1422</v>
+        <v>1.9387</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1422</v>
+        <v>1.9387</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1422</v>
+        <v>1.9387</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1582</v>
+        <v>1.9881</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1582</v>
+        <v>1.9881</v>
       </c>
       <c r="N12" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1061</v>
+        <v>1.8098</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5127</v>
+        <v>0.8389</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0255</v>
+        <v>0.2771</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1061</v>
+        <v>1.8098</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1061</v>
+        <v>1.8098</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1061</v>
+        <v>1.8098</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1216</v>
+        <v>1.8559</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1216</v>
+        <v>1.8559</v>
       </c>
       <c r="N13" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0895</v>
+        <v>1.6314</v>
       </c>
       <c r="C14" t="n">
-        <v>0.505</v>
+        <v>0.7562</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0188</v>
+        <v>0.206</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0895</v>
+        <v>1.6314</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0895</v>
+        <v>1.6314</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0895</v>
+        <v>1.6314</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0997</v>
+        <v>1.7012</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>123</v>
+        <v>222</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0997</v>
+        <v>1.7012</v>
       </c>
       <c r="N14" t="n">
-        <v>123</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.066</v>
+        <v>1.5079</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4941</v>
+        <v>0.699</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.1568</v>
       </c>
       <c r="E15" t="n">
-        <v>1.066</v>
+        <v>1.5079</v>
       </c>
       <c r="F15" t="n">
-        <v>1.066</v>
+        <v>1.5079</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.066</v>
+        <v>1.5079</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0809</v>
+        <v>1.5463</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0809</v>
+        <v>1.5463</v>
       </c>
       <c r="N15" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0427</v>
+        <v>1.4694</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4833</v>
+        <v>0.6811</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0001</v>
+        <v>0.1415</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0427</v>
+        <v>1.4694</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0427</v>
+        <v>1.4694</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0427</v>
+        <v>1.4694</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0573</v>
+        <v>1.4942</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0573</v>
+        <v>1.4942</v>
       </c>
       <c r="N16" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9211</v>
+        <v>1.4452</v>
       </c>
       <c r="C17" t="n">
-        <v>0.427</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0493</v>
+        <v>0.1319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9211</v>
+        <v>1.4452</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9211</v>
+        <v>1.4452</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9211</v>
+        <v>1.4452</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9427</v>
+        <v>1.482</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9427</v>
+        <v>1.482</v>
       </c>
       <c r="N17" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9142</v>
+        <v>1.3869</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4238</v>
+        <v>0.6429</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.052</v>
+        <v>0.1086</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9142</v>
+        <v>1.3869</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9142</v>
+        <v>1.3869</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9142</v>
+        <v>1.3869</v>
       </c>
       <c r="I18" t="n">
-        <v>0.927</v>
+        <v>1.4222</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.927</v>
+        <v>1.4222</v>
       </c>
       <c r="N18" t="n">
         <v>165</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9039</v>
+        <v>1.297</v>
       </c>
       <c r="C19" t="n">
-        <v>0.419</v>
+        <v>0.6012</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0562</v>
+        <v>0.0728</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9039</v>
+        <v>1.297</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9039</v>
+        <v>1.297</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9039</v>
+        <v>1.297</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9251</v>
+        <v>1.33</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9251</v>
+        <v>1.33</v>
       </c>
       <c r="N19" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8238</v>
+        <v>1.0399</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3819</v>
+        <v>0.482</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0886</v>
+        <v>-0.0296</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8238</v>
+        <v>1.0399</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8238</v>
+        <v>1.0399</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8238</v>
+        <v>1.0399</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8354</v>
+        <v>1.0844</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>156</v>
+        <v>222</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8354</v>
+        <v>1.0844</v>
       </c>
       <c r="N20" t="n">
-        <v>156</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5475</v>
+        <v>0.9032</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2538</v>
+        <v>0.4187</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2002</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5475</v>
+        <v>0.9032</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5475</v>
+        <v>0.9032</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5475</v>
+        <v>0.9032</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5526</v>
+        <v>0.9262</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5526</v>
+        <v>0.9262</v>
       </c>
       <c r="N21" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5387</v>
+        <v>0.864</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2497</v>
+        <v>0.4005</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2037</v>
+        <v>-0.0997</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5387</v>
+        <v>0.864</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5387</v>
+        <v>0.864</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5387</v>
+        <v>0.864</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5591</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5591</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>249</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>loWel</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.497</v>
+        <v>0.7361</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2304</v>
+        <v>0.3412</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2206</v>
+        <v>-0.1506</v>
       </c>
       <c r="E23" t="n">
-        <v>0.497</v>
+        <v>0.7361</v>
       </c>
       <c r="F23" t="n">
-        <v>0.497</v>
+        <v>0.7361</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.497</v>
+        <v>0.7361</v>
       </c>
       <c r="I23" t="n">
-        <v>0.497</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.497</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>79</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4014</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1861</v>
+        <v>0.3348</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2592</v>
+        <v>-0.1561</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4014</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4014</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4014</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.407</v>
+        <v>0.7407</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.407</v>
+        <v>0.7407</v>
       </c>
       <c r="N24" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2078</v>
+        <v>0.5853</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0963</v>
+        <v>0.2713</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3374</v>
+        <v>-0.2107</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2078</v>
+        <v>0.5853</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2078</v>
+        <v>0.5853</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2078</v>
+        <v>0.5853</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2107</v>
+        <v>0.5952</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2107</v>
+        <v>0.5952</v>
       </c>
       <c r="N25" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.076</v>
+        <v>0.5621</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0352</v>
+        <v>0.2605</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3907</v>
+        <v>-0.22</v>
       </c>
       <c r="E26" t="n">
-        <v>0.076</v>
+        <v>0.5621</v>
       </c>
       <c r="F26" t="n">
-        <v>0.076</v>
+        <v>0.5621</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.076</v>
+        <v>0.5621</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.5668</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.5668</v>
       </c>
       <c r="N26" t="n">
         <v>87</v>
@@ -1642,216 +1642,216 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>loWel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0514</v>
+        <v>0.497</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0238</v>
+        <v>0.2304</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4421</v>
+        <v>-0.2459</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0514</v>
+        <v>0.497</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0514</v>
+        <v>0.497</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0514</v>
+        <v>0.497</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0519</v>
+        <v>0.497</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0519</v>
+        <v>0.497</v>
       </c>
       <c r="N27" t="n">
-        <v>123</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EasTor</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.177</v>
+        <v>-0.121</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.082</v>
+        <v>-0.0561</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4929</v>
+        <v>-0.4921</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.177</v>
+        <v>-0.121</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.177</v>
+        <v>-0.121</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.177</v>
+        <v>-0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.177</v>
+        <v>-0.1262</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>55</v>
+        <v>222</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.177</v>
+        <v>-0.1262</v>
       </c>
       <c r="N28" t="n">
-        <v>55</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>EasTor</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2111</v>
+        <v>-0.177</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0979</v>
+        <v>-0.082</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5144</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2111</v>
+        <v>-0.177</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2111</v>
+        <v>-0.177</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2111</v>
+        <v>-0.177</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2111</v>
+        <v>-0.177</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2111</v>
+        <v>-0.177</v>
       </c>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6472</v>
+        <v>-0.2111</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3</v>
+        <v>-0.0979</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6828</v>
+        <v>-0.528</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6472</v>
+        <v>-0.2111</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6472</v>
+        <v>-0.2111</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6472</v>
+        <v>-0.2111</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6502</v>
+        <v>-0.2111</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6502</v>
+        <v>-0.2111</v>
       </c>
       <c r="N30" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Hyper</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7074</v>
+        <v>-0.353</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3279</v>
+        <v>-0.1636</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7071</v>
+        <v>-0.5845</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7074</v>
+        <v>-0.353</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7074</v>
+        <v>-0.353</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7074</v>
+        <v>-0.353</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7107</v>
+        <v>-0.356</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7107</v>
+        <v>-0.356</v>
       </c>
       <c r="N31" t="n">
         <v>87</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.723</v>
+        <v>-0.4302</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3351</v>
+        <v>-0.1994</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7134</v>
+        <v>-0.6153</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.723</v>
+        <v>-0.4302</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.723</v>
+        <v>-0.4302</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.723</v>
+        <v>-0.4302</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7297</v>
+        <v>-0.4375</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7297</v>
+        <v>-0.4375</v>
       </c>
       <c r="N32" t="n">
         <v>123</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kairi</t>
+          <t>Hyper</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7587</v>
+        <v>-0.7048</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3517</v>
+        <v>-0.3267</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7279</v>
+        <v>-0.7247</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7587</v>
+        <v>-0.7048</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7587</v>
+        <v>-0.7048</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7587</v>
+        <v>-0.7048</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7587</v>
+        <v>-0.7107</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7587</v>
+        <v>-0.7107</v>
       </c>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Kairi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.908</v>
+        <v>-0.7587</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4209</v>
+        <v>-0.3517</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7882</v>
+        <v>-0.7462</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.908</v>
+        <v>-0.7587</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.908</v>
+        <v>-0.7587</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.908</v>
+        <v>-0.7587</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9293</v>
+        <v>-0.7587</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9293</v>
+        <v>-0.7587</v>
       </c>
       <c r="N34" t="n">
-        <v>222</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2020,7 +2020,7 @@
         <v>-0.4613</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8234</v>
+        <v>-0.8404</v>
       </c>
       <c r="E35" t="n">
         <v>-0.9953</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3174</v>
+        <v>-1.3125</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6107</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9536</v>
+        <v>-0.9668</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3174</v>
+        <v>-1.3125</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3174</v>
+        <v>-1.3125</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3174</v>
+        <v>-1.3125</v>
       </c>
       <c r="I36" t="n">
         <v>-1.3235</v>
@@ -2112,7 +2112,7 @@
         <v>-0.6146</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.957</v>
+        <v>-0.9722</v>
       </c>
       <c r="E37" t="n">
         <v>-1.326</v>
@@ -2158,7 +2158,7 @@
         <v>-0.7174</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0466</v>
+        <v>-1.0605</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5476</v>
@@ -2204,7 +2204,7 @@
         <v>-0.8108</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.128</v>
+        <v>-1.1408</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7492</v>
@@ -2250,7 +2250,7 @@
         <v>-0.8424</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1555</v>
+        <v>-1.1679</v>
       </c>
       <c r="E40" t="n">
         <v>-1.8173</v>
@@ -2296,7 +2296,7 @@
         <v>-1.2166</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4817</v>
+        <v>-1.4896</v>
       </c>
       <c r="E41" t="n">
         <v>-2.6247</v>

--- a/database/event/2100/event_2100_evp_summary.xlsx
+++ b/database/event/2100/event_2100_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.3599</v>
+        <v>3.4177</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0209</v>
+        <v>1.5842</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2931</v>
+        <v>0.9049</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3599</v>
+        <v>3.4177</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3599</v>
+        <v>3.4177</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5333</v>
+        <v>4.1449</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7273</v>
+        <v>5.0703</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.7273</v>
+        <v>5.0703</v>
       </c>
       <c r="N2" t="n">
         <v>222</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3415</v>
+        <v>3.2526</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0124</v>
+        <v>1.5077</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2857</v>
+        <v>0.8304</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3415</v>
+        <v>3.2526</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3415</v>
+        <v>3.2526</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5044</v>
+        <v>3.7823</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8167</v>
+        <v>5.2214</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8167</v>
+        <v>5.2214</v>
       </c>
       <c r="N3" t="n">
         <v>249</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1184</v>
+        <v>3.2034</v>
       </c>
       <c r="C4" t="n">
-        <v>1.909</v>
+        <v>1.4849</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1969</v>
+        <v>0.8082</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1184</v>
+        <v>3.2034</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1184</v>
+        <v>3.2034</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1545</v>
+        <v>3.6745</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3323</v>
+        <v>4.4948</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3323</v>
+        <v>4.4948</v>
       </c>
       <c r="N4" t="n">
         <v>222</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7849</v>
+        <v>3.0666</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7544</v>
+        <v>1.4215</v>
       </c>
       <c r="D5" t="n">
-        <v>1.064</v>
+        <v>0.7464</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7849</v>
+        <v>3.0666</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7849</v>
+        <v>3.0666</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7849</v>
+        <v>3.3741</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0474</v>
+        <v>4.6578</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0474</v>
+        <v>4.6578</v>
       </c>
       <c r="N5" t="n">
         <v>249</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5248</v>
+        <v>2.972</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6338</v>
+        <v>1.3776</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9604</v>
+        <v>0.7037</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5248</v>
+        <v>2.972</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5248</v>
+        <v>2.972</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5248</v>
+        <v>3.1662</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6146</v>
+        <v>3.5732</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6146</v>
+        <v>3.5732</v>
       </c>
       <c r="N6" t="n">
         <v>165</v>
@@ -722,185 +722,185 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9376</v>
+        <v>2.562</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3617</v>
+        <v>1.1876</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7264</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9376</v>
+        <v>2.562</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9376</v>
+        <v>2.562</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9376</v>
+        <v>2.562</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1413</v>
+        <v>2.7771</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1413</v>
+        <v>2.7771</v>
       </c>
       <c r="N7" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4584</v>
+        <v>2.3693</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1395</v>
+        <v>1.0982</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5355</v>
+        <v>0.4316</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4584</v>
+        <v>2.3693</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4584</v>
+        <v>2.3693</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4584</v>
+        <v>2.3693</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5</v>
+        <v>3.2707</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5</v>
+        <v>3.2707</v>
       </c>
       <c r="N8" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3438</v>
+        <v>2.1679</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0864</v>
+        <v>1.0049</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4899</v>
+        <v>0.3407</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3438</v>
+        <v>2.1679</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3438</v>
+        <v>2.1679</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3438</v>
+        <v>2.1679</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5063</v>
+        <v>2.2571</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>249</v>
+        <v>87</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5063</v>
+        <v>2.2571</v>
       </c>
       <c r="N9" t="n">
-        <v>249</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.097</v>
+        <v>2.1274</v>
       </c>
       <c r="C10" t="n">
-        <v>0.972</v>
+        <v>0.9861</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3915</v>
+        <v>0.3224</v>
       </c>
       <c r="E10" t="n">
-        <v>2.097</v>
+        <v>2.1274</v>
       </c>
       <c r="F10" t="n">
-        <v>2.097</v>
+        <v>2.1274</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.097</v>
+        <v>2.1274</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1146</v>
+        <v>2.9368</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>87</v>
+        <v>249</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1146</v>
+        <v>2.9368</v>
       </c>
       <c r="N10" t="n">
-        <v>87</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0585</v>
+        <v>2.1019</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9542</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3762</v>
+        <v>0.3109</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0585</v>
+        <v>2.1019</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0585</v>
+        <v>2.1019</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0585</v>
+        <v>2.1019</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1109</v>
+        <v>2.3721</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1109</v>
+        <v>2.3721</v>
       </c>
       <c r="N11" t="n">
         <v>156</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9387</v>
+        <v>2.0244</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8986</v>
+        <v>0.9384</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3285</v>
+        <v>0.2759</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9387</v>
+        <v>2.0244</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9387</v>
+        <v>2.0244</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9387</v>
+        <v>2.0244</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9881</v>
+        <v>2.2846</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9881</v>
+        <v>2.2846</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -998,323 +998,323 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8098</v>
+        <v>1.7519</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8389</v>
+        <v>0.8121</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2771</v>
+        <v>0.1529</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8098</v>
+        <v>1.7519</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8098</v>
+        <v>1.7519</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8098</v>
+        <v>1.7519</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8559</v>
+        <v>2.143</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>165</v>
+        <v>222</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8559</v>
+        <v>2.143</v>
       </c>
       <c r="N13" t="n">
-        <v>165</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6314</v>
+        <v>1.6939</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7562</v>
+        <v>0.7852</v>
       </c>
       <c r="D14" t="n">
-        <v>0.206</v>
+        <v>0.1267</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6314</v>
+        <v>1.6939</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6314</v>
+        <v>1.6939</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6314</v>
+        <v>1.6939</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7012</v>
+        <v>1.9116</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>222</v>
+        <v>165</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7012</v>
+        <v>1.9116</v>
       </c>
       <c r="N14" t="n">
-        <v>222</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5079</v>
+        <v>1.6559</v>
       </c>
       <c r="C15" t="n">
-        <v>0.699</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1568</v>
+        <v>0.1095</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5079</v>
+        <v>1.6559</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5079</v>
+        <v>1.6559</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5079</v>
+        <v>1.6559</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5463</v>
+        <v>1.8687</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5463</v>
+        <v>1.8687</v>
       </c>
       <c r="N15" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4694</v>
+        <v>1.5859</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6811</v>
+        <v>0.7351</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1415</v>
+        <v>0.0779</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4694</v>
+        <v>1.5859</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4694</v>
+        <v>1.5859</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4694</v>
+        <v>1.5859</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4942</v>
+        <v>1.7897</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4942</v>
+        <v>1.7897</v>
       </c>
       <c r="N16" t="n">
-        <v>123</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4452</v>
+        <v>1.5459</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.7166</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1319</v>
+        <v>0.0599</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4452</v>
+        <v>1.5459</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4452</v>
+        <v>1.5459</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4452</v>
+        <v>1.5459</v>
       </c>
       <c r="I17" t="n">
-        <v>1.482</v>
+        <v>1.7446</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.482</v>
+        <v>1.7446</v>
       </c>
       <c r="N17" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3869</v>
+        <v>1.476</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6429</v>
+        <v>0.6842</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1086</v>
+        <v>0.0283</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3869</v>
+        <v>1.476</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3869</v>
+        <v>1.476</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3869</v>
+        <v>1.476</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4222</v>
+        <v>1.6657</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4222</v>
+        <v>1.6657</v>
       </c>
       <c r="N18" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.297</v>
+        <v>1.4421</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6012</v>
+        <v>0.6685</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0728</v>
+        <v>0.013</v>
       </c>
       <c r="E19" t="n">
-        <v>1.297</v>
+        <v>1.4421</v>
       </c>
       <c r="F19" t="n">
-        <v>1.297</v>
+        <v>1.4421</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.297</v>
+        <v>1.4421</v>
       </c>
       <c r="I19" t="n">
-        <v>1.33</v>
+        <v>1.5632</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.33</v>
+        <v>1.5632</v>
       </c>
       <c r="N19" t="n">
-        <v>156</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0399</v>
+        <v>1.2495</v>
       </c>
       <c r="C20" t="n">
-        <v>0.482</v>
+        <v>0.5792</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0296</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0399</v>
+        <v>1.2495</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0399</v>
+        <v>1.2495</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0399</v>
+        <v>1.2495</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0844</v>
+        <v>1.5284</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0844</v>
+        <v>1.5284</v>
       </c>
       <c r="N20" t="n">
         <v>222</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9032</v>
+        <v>1.1636</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4187</v>
+        <v>0.5394</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1127</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9032</v>
+        <v>1.1636</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9032</v>
+        <v>1.1636</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9032</v>
+        <v>1.1636</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9262</v>
+        <v>1.3132</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9262</v>
+        <v>1.3132</v>
       </c>
       <c r="N21" t="n">
         <v>156</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.864</v>
+        <v>1.0129</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4005</v>
+        <v>0.4695</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0997</v>
+        <v>-0.1807</v>
       </c>
       <c r="E22" t="n">
-        <v>0.864</v>
+        <v>1.0129</v>
       </c>
       <c r="F22" t="n">
-        <v>0.864</v>
+        <v>1.0129</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.864</v>
+        <v>1.0129</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9239000000000001</v>
+        <v>1.0979</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9239000000000001</v>
+        <v>1.0979</v>
       </c>
       <c r="N22" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7361</v>
+        <v>0.9605</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3412</v>
+        <v>0.4452</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1506</v>
+        <v>-0.2044</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7361</v>
+        <v>0.9605</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7361</v>
+        <v>0.9605</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7361</v>
+        <v>0.9605</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7485000000000001</v>
+        <v>1.0839</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7485000000000001</v>
+        <v>1.0839</v>
       </c>
       <c r="N23" t="n">
-        <v>123</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.9256</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3348</v>
+        <v>0.429</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1561</v>
+        <v>-0.2202</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.9256</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.9256</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.9256</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7407</v>
+        <v>1.0033</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7407</v>
+        <v>1.0033</v>
       </c>
       <c r="N24" t="n">
-        <v>165</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5853</v>
+        <v>0.8702</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2713</v>
+        <v>0.4034</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2107</v>
+        <v>-0.2452</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5853</v>
+        <v>0.8702</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5853</v>
+        <v>0.8702</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5853</v>
+        <v>0.8702</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5952</v>
+        <v>1.2013</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5952</v>
+        <v>1.2013</v>
       </c>
       <c r="N25" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5621</v>
+        <v>0.8206</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2605</v>
+        <v>0.3804</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.22</v>
+        <v>-0.2676</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5621</v>
+        <v>0.8206</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5621</v>
+        <v>0.8206</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5621</v>
+        <v>0.8206</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5668</v>
+        <v>0.8544</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5668</v>
+        <v>0.8544</v>
       </c>
       <c r="N26" t="n">
         <v>87</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.497</v>
+        <v>0.6056</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2304</v>
+        <v>0.2807</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2459</v>
+        <v>-0.3646</v>
       </c>
       <c r="E27" t="n">
-        <v>0.497</v>
+        <v>0.6056</v>
       </c>
       <c r="F27" t="n">
-        <v>0.497</v>
+        <v>0.6056</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.497</v>
+        <v>0.6056</v>
       </c>
       <c r="I27" t="n">
-        <v>0.497</v>
+        <v>0.6056</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.497</v>
+        <v>0.6056</v>
       </c>
       <c r="N27" t="n">
         <v>79</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.121</v>
+        <v>0.1017</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0561</v>
+        <v>0.0471</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4921</v>
+        <v>-0.5921</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.121</v>
+        <v>0.1017</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.121</v>
+        <v>0.1017</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.121</v>
+        <v>0.1017</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1262</v>
+        <v>0.1059</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>222</v>
+        <v>87</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1262</v>
+        <v>0.1059</v>
       </c>
       <c r="N28" t="n">
-        <v>222</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EasTor</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.177</v>
+        <v>0.066</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.082</v>
+        <v>0.0306</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5144</v>
+        <v>-0.6082</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.177</v>
+        <v>0.066</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.177</v>
+        <v>0.066</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.177</v>
+        <v>0.066</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.177</v>
+        <v>0.0808</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>55</v>
+        <v>222</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.177</v>
+        <v>0.0808</v>
       </c>
       <c r="N29" t="n">
-        <v>55</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2111</v>
+        <v>0.0421</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0979</v>
+        <v>0.0195</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.528</v>
+        <v>-0.619</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2111</v>
+        <v>0.0421</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2111</v>
+        <v>0.0421</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2111</v>
+        <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2111</v>
+        <v>0.0421</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2111</v>
+        <v>0.0421</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>EasTor</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.353</v>
+        <v>-0.0313</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1636</v>
+        <v>-0.0145</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5845</v>
+        <v>-0.6521</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.353</v>
+        <v>-0.0313</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.353</v>
+        <v>-0.0313</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.353</v>
+        <v>-0.0313</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.356</v>
+        <v>-0.0313</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.356</v>
+        <v>-0.0313</v>
       </c>
       <c r="N31" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4302</v>
+        <v>-0.1324</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1994</v>
+        <v>-0.0614</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6153</v>
+        <v>-0.6978</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4302</v>
+        <v>-0.1324</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4302</v>
+        <v>-0.1324</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4302</v>
+        <v>-0.1324</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4375</v>
+        <v>-0.1435</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4375</v>
+        <v>-0.1435</v>
       </c>
       <c r="N32" t="n">
         <v>123</v>
@@ -1918,185 +1918,185 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hyper</t>
+          <t>Kairi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7048</v>
+        <v>-0.3715</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3267</v>
+        <v>-0.1722</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7247</v>
+        <v>-0.8057</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7048</v>
+        <v>-0.3715</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7048</v>
+        <v>-0.3715</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7048</v>
+        <v>-0.3715</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7107</v>
+        <v>-0.3715</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7107</v>
+        <v>-0.3715</v>
       </c>
       <c r="N33" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kairi</t>
+          <t>Hyper</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7587</v>
+        <v>-0.391</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3517</v>
+        <v>-0.1812</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7462</v>
+        <v>-0.8145</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7587</v>
+        <v>-0.391</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7587</v>
+        <v>-0.391</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7587</v>
+        <v>-0.391</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7587</v>
+        <v>-0.4071</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7587</v>
+        <v>-0.4071</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kanarito</t>
+          <t>repo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9953</v>
+        <v>-0.579</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4613</v>
+        <v>-0.2684</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8404</v>
+        <v>-0.8994</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9953</v>
+        <v>-0.579</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9953</v>
+        <v>-0.579</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9953</v>
+        <v>-0.579</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9953</v>
+        <v>-0.6028</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9953</v>
+        <v>-0.6028</v>
       </c>
       <c r="N35" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>repo</t>
+          <t>kanarito</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3125</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.3166</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9668</v>
+        <v>-0.9464</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3125</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3125</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3125</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3235</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3235</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.326</v>
+        <v>-0.9991</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6146</v>
+        <v>-0.4631</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9722</v>
+        <v>-1.0891</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.326</v>
+        <v>-0.9991</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.326</v>
+        <v>-0.9991</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.326</v>
+        <v>-0.9991</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.326</v>
+        <v>-0.9991</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.326</v>
+        <v>-0.9991</v>
       </c>
       <c r="N37" t="n">
         <v>55</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5476</v>
+        <v>-1.1286</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.7174</v>
+        <v>-0.5231</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0605</v>
+        <v>-1.1475</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5476</v>
+        <v>-1.1286</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5476</v>
+        <v>-1.1286</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5476</v>
+        <v>-1.1286</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5476</v>
+        <v>-1.1286</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5476</v>
+        <v>-1.1286</v>
       </c>
       <c r="N38" t="n">
         <v>55</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7492</v>
+        <v>-1.1591</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.8108</v>
+        <v>-0.5373</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1408</v>
+        <v>-1.1613</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7492</v>
+        <v>-1.1591</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7492</v>
+        <v>-1.1591</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7492</v>
+        <v>-1.1591</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7492</v>
+        <v>-1.1591</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7492</v>
+        <v>-1.1591</v>
       </c>
       <c r="N39" t="n">
         <v>79</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8173</v>
+        <v>-1.2963</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8424</v>
+        <v>-0.6009</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1679</v>
+        <v>-1.2232</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8173</v>
+        <v>-1.2963</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8173</v>
+        <v>-1.2963</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8173</v>
+        <v>-1.2963</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8173</v>
+        <v>-1.2963</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8173</v>
+        <v>-1.2963</v>
       </c>
       <c r="N40" t="n">
         <v>55</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6247</v>
+        <v>-1.8741</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.2166</v>
+        <v>-0.8687</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4896</v>
+        <v>-1.4841</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6247</v>
+        <v>-1.8741</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6247</v>
+        <v>-1.8741</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6247</v>
+        <v>-1.8741</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.6247</v>
+        <v>-1.8741</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.6247</v>
+        <v>-1.8741</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2429,10 +2429,10 @@
         <v>1.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2007</v>
+        <v>0.2098</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8203</v>
+        <v>6.0842</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1019</v>
+        <v>0.0956</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9551</v>
+        <v>2.7724</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1048</v>
+        <v>-0.0614</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.0392</v>
+        <v>-1.7806</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1265</v>
+        <v>-0.074</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.6685</v>
+        <v>-2.146</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2552</v>
+        <v>-0.1539</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.4008</v>
+        <v>-4.4631</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3233</v>
+        <v>1.2045</v>
       </c>
       <c r="J7" t="n">
-        <v>38.3757</v>
+        <v>34.9305</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0384</v>
+        <v>1.0173</v>
       </c>
       <c r="J8" t="n">
-        <v>30.1136</v>
+        <v>29.5017</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1059</v>
+        <v>-0.0374</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0711</v>
+        <v>-1.0846</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2799</v>
+        <v>-0.2057</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.117100000000001</v>
+        <v>-5.9653</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5171</v>
+        <v>-0.4493</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.9959</v>
+        <v>-13.0297</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7482</v>
+        <v>0.9303</v>
       </c>
       <c r="J12" t="n">
-        <v>22.446</v>
+        <v>27.909</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1245</v>
+        <v>0.1206</v>
       </c>
       <c r="J13" t="n">
-        <v>3.735</v>
+        <v>3.618</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1036</v>
+        <v>-0.0613</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.108</v>
+        <v>-1.839</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4352</v>
+        <v>-0.276</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.056</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5805</v>
+        <v>-0.3807</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.415</v>
+        <v>-11.421</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8456</v>
+        <v>0.8181</v>
       </c>
       <c r="J17" t="n">
-        <v>25.368</v>
+        <v>24.543</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.524</v>
+        <v>0.4919</v>
       </c>
       <c r="J18" t="n">
-        <v>15.72</v>
+        <v>14.757</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.1179</v>
       </c>
       <c r="J19" t="n">
-        <v>2.61</v>
+        <v>3.537</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3687</v>
+        <v>-0.3082</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.061</v>
+        <v>-9.246</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3687</v>
+        <v>-0.3082</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.061</v>
+        <v>-9.246</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3618</v>
+        <v>1.2395</v>
       </c>
       <c r="J22" t="n">
-        <v>32.6832</v>
+        <v>29.748</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0613</v>
+        <v>1.0541</v>
       </c>
       <c r="J23" t="n">
-        <v>25.4712</v>
+        <v>25.2984</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.35</v>
       </c>
       <c r="I24" t="n">
-        <v>0.837</v>
+        <v>0.878</v>
       </c>
       <c r="J24" t="n">
-        <v>20.088</v>
+        <v>21.072</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.32</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7573</v>
+        <v>0.8137</v>
       </c>
       <c r="J25" t="n">
-        <v>18.1752</v>
+        <v>19.5288</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5857</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.0568</v>
+        <v>-12.3744</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.24</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5308</v>
+        <v>0.6337</v>
       </c>
       <c r="J27" t="n">
-        <v>12.7392</v>
+        <v>15.2088</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.79</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2916</v>
+        <v>-0.2215</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.9984</v>
+        <v>-5.316</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3096</v>
+        <v>-0.2311</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.4304</v>
+        <v>-5.5464</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.4461</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.9312</v>
+        <v>-10.7064</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.5294</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.6408</v>
+        <v>-12.7056</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4492</v>
+        <v>1.2966</v>
       </c>
       <c r="J32" t="n">
-        <v>33.3316</v>
+        <v>29.8218</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.56</v>
       </c>
       <c r="I33" t="n">
-        <v>1.277</v>
+        <v>1.1876</v>
       </c>
       <c r="J33" t="n">
-        <v>29.371</v>
+        <v>27.3148</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6775</v>
       </c>
       <c r="J34" t="n">
-        <v>13.5056</v>
+        <v>15.5825</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.24</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6307</v>
       </c>
       <c r="J35" t="n">
-        <v>12.3924</v>
+        <v>14.5061</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3343</v>
+        <v>-0.2488</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.6889</v>
+        <v>-5.7224</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.99</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0849</v>
+        <v>0.0437</v>
       </c>
       <c r="J37" t="n">
-        <v>1.9527</v>
+        <v>1.0051</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2628</v>
+        <v>-0.2086</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.0444</v>
+        <v>-4.7978</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.68</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4768</v>
+        <v>-0.3213</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.9664</v>
+        <v>-7.3899</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.3588</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.3234</v>
+        <v>-8.2524</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.578</v>
+        <v>-0.3869</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.294</v>
+        <v>-8.8987</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.09</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2176</v>
+        <v>0.2304</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0928</v>
+        <v>6.4512</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.051</v>
+        <v>0.0405</v>
       </c>
       <c r="J43" t="n">
-        <v>1.428</v>
+        <v>1.134</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.023</v>
+        <v>-0.0195</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.644</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1674</v>
+        <v>-0.0982</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.6872</v>
+        <v>-2.7496</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2391</v>
+        <v>-0.1432</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.6948</v>
+        <v>-4.0096</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.97</v>
       </c>
       <c r="I47" t="n">
-        <v>2.0097</v>
+        <v>1.7213</v>
       </c>
       <c r="J47" t="n">
-        <v>56.2716</v>
+        <v>48.1964</v>
       </c>
     </row>
     <row r="48">
@@ -4309,10 +4309,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1486</v>
+        <v>0.2159</v>
       </c>
       <c r="J49" t="n">
-        <v>4.1608</v>
+        <v>6.0452</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.681</v>
+        <v>-0.6221</v>
       </c>
       <c r="J50" t="n">
-        <v>-19.068</v>
+        <v>-17.4188</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7758</v>
+        <v>-0.7254</v>
       </c>
       <c r="J51" t="n">
-        <v>-21.7224</v>
+        <v>-20.3112</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8025</v>
+        <v>0.8105</v>
       </c>
       <c r="J52" t="n">
-        <v>21.6675</v>
+        <v>21.8835</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7788</v>
+        <v>0.7877</v>
       </c>
       <c r="J53" t="n">
-        <v>21.0276</v>
+        <v>21.2679</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7054</v>
+        <v>0.719</v>
       </c>
       <c r="J54" t="n">
-        <v>19.0458</v>
+        <v>19.413</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.16</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3923</v>
+        <v>0.4581</v>
       </c>
       <c r="J55" t="n">
-        <v>10.5921</v>
+        <v>12.3687</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.07</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1373</v>
+        <v>0.2096</v>
       </c>
       <c r="J56" t="n">
-        <v>3.7071</v>
+        <v>5.6592</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2097</v>
+        <v>0.2024</v>
       </c>
       <c r="J57" t="n">
-        <v>5.6619</v>
+        <v>5.4648</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0362</v>
+        <v>-0.0487</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.9774</v>
+        <v>-1.3149</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3262</v>
+        <v>-0.2125</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.807399999999999</v>
+        <v>-5.7375</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4039</v>
+        <v>-0.2616</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.9053</v>
+        <v>-7.0632</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4477</v>
+        <v>-0.2907</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.0879</v>
+        <v>-7.8489</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.63</v>
       </c>
       <c r="I62" t="n">
-        <v>1.391</v>
+        <v>1.2634</v>
       </c>
       <c r="J62" t="n">
-        <v>31.993</v>
+        <v>29.0582</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0926</v>
+        <v>1.0825</v>
       </c>
       <c r="J63" t="n">
-        <v>25.1298</v>
+        <v>24.8975</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.48</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0926</v>
+        <v>1.0825</v>
       </c>
       <c r="J64" t="n">
-        <v>25.1298</v>
+        <v>24.8975</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6827</v>
+        <v>0.7822</v>
       </c>
       <c r="J65" t="n">
-        <v>15.7021</v>
+        <v>17.9906</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.177</v>
+        <v>-0.0907</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.071</v>
+        <v>-2.0861</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.31</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6544</v>
+        <v>0.8259</v>
       </c>
       <c r="J67" t="n">
-        <v>15.0512</v>
+        <v>18.9957</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.305</v>
+        <v>-0.2413</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.015</v>
+        <v>-5.5499</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.62</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.5481</v>
+        <v>-0.3709</v>
       </c>
       <c r="J69" t="n">
-        <v>-12.6063</v>
+        <v>-8.5307</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.46</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7637</v>
+        <v>-0.5205</v>
       </c>
       <c r="J70" t="n">
-        <v>-17.5651</v>
+        <v>-11.9715</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.36</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8863</v>
+        <v>-0.6137</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.3849</v>
+        <v>-14.1151</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3895</v>
+        <v>0.4353</v>
       </c>
       <c r="J72" t="n">
-        <v>11.2955</v>
+        <v>12.6237</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0567</v>
+        <v>-0.0618</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.6443</v>
+        <v>-1.7922</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0765</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.2185</v>
+        <v>-2.1576</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.66</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5443</v>
+        <v>-0.3573</v>
       </c>
       <c r="J75" t="n">
-        <v>-15.7847</v>
+        <v>-10.3617</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6224</v>
+        <v>-0.4135</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.0496</v>
+        <v>-11.9915</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3433</v>
+        <v>1.2216</v>
       </c>
       <c r="J77" t="n">
-        <v>38.9557</v>
+        <v>35.4264</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4661</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>13.5169</v>
+        <v>15.3903</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4661</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>13.5169</v>
+        <v>15.3903</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4124</v>
+        <v>0.4809</v>
       </c>
       <c r="J80" t="n">
-        <v>11.9596</v>
+        <v>13.9461</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.05</v>
       </c>
       <c r="I81" t="n">
-        <v>0.0699</v>
+        <v>0.144</v>
       </c>
       <c r="J81" t="n">
-        <v>2.0271</v>
+        <v>4.176</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.78</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6624</v>
+        <v>1.4384</v>
       </c>
       <c r="J82" t="n">
-        <v>34.9104</v>
+        <v>30.2064</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.62</v>
       </c>
       <c r="I83" t="n">
-        <v>1.3684</v>
+        <v>1.2501</v>
       </c>
       <c r="J83" t="n">
-        <v>28.7364</v>
+        <v>26.2521</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9069</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>19.0449</v>
+        <v>20.3112</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.09</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1392</v>
+        <v>0.2306</v>
       </c>
       <c r="J85" t="n">
-        <v>2.9232</v>
+        <v>4.8426</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.0217</v>
+        <v>0.1085</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4557</v>
+        <v>2.2785</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.23</v>
       </c>
       <c r="I87" t="n">
-        <v>0.527</v>
+        <v>0.6308</v>
       </c>
       <c r="J87" t="n">
-        <v>11.067</v>
+        <v>13.2468</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0174</v>
+        <v>-0.0222</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3654</v>
+        <v>-0.4662</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.5911</v>
+        <v>-0.396</v>
       </c>
       <c r="J89" t="n">
-        <v>-12.4131</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.53</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6841</v>
+        <v>-0.4614</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.3661</v>
+        <v>-9.689399999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8571</v>
+        <v>-0.5911</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.9991</v>
+        <v>-12.4131</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.01</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0961</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>2.4025</v>
+        <v>1.655</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0265</v>
+        <v>-0.0069</v>
       </c>
       <c r="J93" t="n">
-        <v>0.6625</v>
+        <v>-0.1725</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.97</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0217</v>
+        <v>-0.0376</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.5425</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4382</v>
+        <v>-0.2831</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.955</v>
+        <v>-7.0775</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5079</v>
+        <v>-0.3311</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.6975</v>
+        <v>-8.2775</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.68</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5338</v>
+        <v>1.348</v>
       </c>
       <c r="J97" t="n">
-        <v>38.345</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.64</v>
       </c>
       <c r="I98" t="n">
-        <v>1.4596</v>
+        <v>1.2993</v>
       </c>
       <c r="J98" t="n">
-        <v>36.49</v>
+        <v>32.4825</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0104</v>
+        <v>0.0674</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.26</v>
+        <v>1.685</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.02</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0474</v>
+        <v>0.0302</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.185</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2462</v>
+        <v>-0.1619</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.155</v>
+        <v>-4.0475</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.19</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5995</v>
+        <v>0.5676</v>
       </c>
       <c r="J102" t="n">
-        <v>21.582</v>
+        <v>20.4336</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5995</v>
+        <v>0.5676</v>
       </c>
       <c r="J103" t="n">
-        <v>21.582</v>
+        <v>20.4336</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4361</v>
+        <v>0.4105</v>
       </c>
       <c r="J104" t="n">
-        <v>15.6996</v>
+        <v>14.778</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2422</v>
+        <v>-0.1828</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.719200000000001</v>
+        <v>-6.5808</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.88</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4864</v>
+        <v>-0.426</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.5104</v>
+        <v>-15.336</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5538</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J107" t="n">
-        <v>19.9368</v>
+        <v>23.9688</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3353</v>
+        <v>0.3866</v>
       </c>
       <c r="J108" t="n">
-        <v>12.0708</v>
+        <v>13.9176</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.03</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0547</v>
+        <v>0.0848</v>
       </c>
       <c r="J109" t="n">
-        <v>1.9692</v>
+        <v>3.0528</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2758</v>
+        <v>-0.1622</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.928800000000001</v>
+        <v>-5.8392</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.84</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3373</v>
+        <v>-0.2045</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.1428</v>
+        <v>-7.362</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.69</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5804</v>
+        <v>1.3772</v>
       </c>
       <c r="J112" t="n">
-        <v>39.51</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.27</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7134</v>
+        <v>0.7217</v>
       </c>
       <c r="J113" t="n">
-        <v>17.835</v>
+        <v>18.0425</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1424</v>
+        <v>0.2125</v>
       </c>
       <c r="J114" t="n">
-        <v>3.56</v>
+        <v>5.3125</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1114</v>
+        <v>0.1817</v>
       </c>
       <c r="J115" t="n">
-        <v>2.785</v>
+        <v>4.5425</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.96</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.299</v>
+        <v>-0.2195</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.475</v>
+        <v>-5.4875</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3223</v>
+        <v>0.3476</v>
       </c>
       <c r="J117" t="n">
-        <v>8.057499999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2395</v>
+        <v>0.2416</v>
       </c>
       <c r="J118" t="n">
-        <v>5.9875</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1212</v>
+        <v>0.096</v>
       </c>
       <c r="J119" t="n">
-        <v>3.03</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.75</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4237</v>
+        <v>-0.2735</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.5925</v>
+        <v>-6.8375</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.42</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.8414</v>
+        <v>-0.5793</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.035</v>
+        <v>-14.4825</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.88</v>
       </c>
       <c r="I122" t="n">
-        <v>1.7762</v>
+        <v>1.522</v>
       </c>
       <c r="J122" t="n">
-        <v>35.524</v>
+        <v>30.44</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.58</v>
       </c>
       <c r="I123" t="n">
-        <v>1.2169</v>
+        <v>1.1826</v>
       </c>
       <c r="J123" t="n">
-        <v>24.338</v>
+        <v>23.652</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.53</v>
       </c>
       <c r="I124" t="n">
-        <v>1.0948</v>
+        <v>1.1261</v>
       </c>
       <c r="J124" t="n">
-        <v>21.896</v>
+        <v>22.522</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.47</v>
       </c>
       <c r="I125" t="n">
-        <v>0.9611</v>
+        <v>1.0555</v>
       </c>
       <c r="J125" t="n">
-        <v>19.222</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.23</v>
       </c>
       <c r="I126" t="n">
-        <v>0.4452</v>
+        <v>0.5649</v>
       </c>
       <c r="J126" t="n">
-        <v>8.904</v>
+        <v>11.298</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.8</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.2196</v>
+        <v>-0.1909</v>
       </c>
       <c r="J127" t="n">
-        <v>-4.392</v>
+        <v>-3.818</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2669</v>
+        <v>-0.2226</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.338</v>
+        <v>-4.452</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3792</v>
+        <v>-0.2925</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.584</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5596</v>
+        <v>-0.3829</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.192</v>
+        <v>-7.658</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7794</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.588</v>
+        <v>-10.656</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.72</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4936</v>
+        <v>1.343</v>
       </c>
       <c r="J132" t="n">
-        <v>28.3784</v>
+        <v>25.517</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.66</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3805</v>
+        <v>1.2747</v>
       </c>
       <c r="J133" t="n">
-        <v>26.2295</v>
+        <v>24.2193</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9856</v>
+        <v>1.0683</v>
       </c>
       <c r="J134" t="n">
-        <v>18.7264</v>
+        <v>20.2977</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.46</v>
       </c>
       <c r="I135" t="n">
-        <v>0.9426</v>
+        <v>1.0434</v>
       </c>
       <c r="J135" t="n">
-        <v>17.9094</v>
+        <v>19.8246</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.34</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6881</v>
+        <v>0.8196</v>
       </c>
       <c r="J136" t="n">
-        <v>13.0739</v>
+        <v>15.5724</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.2107</v>
+        <v>-0.1881</v>
       </c>
       <c r="J137" t="n">
-        <v>-4.0033</v>
+        <v>-3.5739</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.75</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2729</v>
+        <v>-0.2313</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.1851</v>
+        <v>-4.3947</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.55</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.4212</v>
       </c>
       <c r="J139" t="n">
-        <v>-11.6356</v>
+        <v>-8.002800000000001</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.54</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6273</v>
+        <v>-0.4305</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.9187</v>
+        <v>-8.179500000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7533</v>
+        <v>-0.5153</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.3127</v>
+        <v>-9.790699999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6891</v>
+        <v>1.4508</v>
       </c>
       <c r="J142" t="n">
-        <v>48.9839</v>
+        <v>42.0732</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.3</v>
       </c>
       <c r="I143" t="n">
-        <v>0.786</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J143" t="n">
-        <v>22.794</v>
+        <v>22.9332</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3718</v>
+        <v>0.435</v>
       </c>
       <c r="J144" t="n">
-        <v>10.7822</v>
+        <v>12.615</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.03</v>
       </c>
       <c r="I145" t="n">
-        <v>0.011</v>
+        <v>0.082</v>
       </c>
       <c r="J145" t="n">
-        <v>0.319</v>
+        <v>2.378</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6845</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-19.8505</v>
+        <v>-18.1395</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.22</v>
       </c>
       <c r="I147" t="n">
-        <v>0.439</v>
+        <v>0.504</v>
       </c>
       <c r="J147" t="n">
-        <v>12.731</v>
+        <v>14.616</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.16</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3519</v>
+        <v>0.3897</v>
       </c>
       <c r="J148" t="n">
-        <v>10.2051</v>
+        <v>11.3013</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3483</v>
+        <v>-0.2198</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.1007</v>
+        <v>-6.3742</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.74</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4502</v>
+        <v>-0.2888</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.0558</v>
+        <v>-8.3752</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5182</v>
+        <v>-0.3367</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.0278</v>
+        <v>-9.7643</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.33</v>
       </c>
       <c r="I152" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J152" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.64</v>
       </c>
       <c r="I153" t="n">
-        <v>1.3251</v>
+        <v>1.248</v>
       </c>
       <c r="J153" t="n">
-        <v>23.8518</v>
+        <v>22.464</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.54</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0973</v>
+        <v>1.1355</v>
       </c>
       <c r="J154" t="n">
-        <v>19.7514</v>
+        <v>20.439</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.25</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4827</v>
+        <v>0.6071</v>
       </c>
       <c r="J155" t="n">
-        <v>8.688599999999999</v>
+        <v>10.9278</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0415</v>
+        <v>0.1355</v>
       </c>
       <c r="J156" t="n">
-        <v>0.747</v>
+        <v>2.439</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3894</v>
+        <v>0.4529</v>
       </c>
       <c r="J157" t="n">
-        <v>7.0092</v>
+        <v>8.152200000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.68</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3887</v>
+        <v>-0.3048</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.9966</v>
+        <v>-5.4864</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.5023</v>
+        <v>-0.3594</v>
       </c>
       <c r="J159" t="n">
-        <v>-9.041399999999999</v>
+        <v>-6.4692</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.53</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6464</v>
+        <v>-0.4417</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.6352</v>
+        <v>-7.9506</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.2</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.0634</v>
+        <v>-0.7553</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.1412</v>
+        <v>-13.5954</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.09</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2368</v>
+        <v>0.2449</v>
       </c>
       <c r="J162" t="n">
-        <v>6.8672</v>
+        <v>7.1021</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1829</v>
+        <v>0.1791</v>
       </c>
       <c r="J163" t="n">
-        <v>5.3041</v>
+        <v>5.1939</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.98</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0222</v>
+        <v>-0.0303</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.6438</v>
+        <v>-0.8787</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2881</v>
+        <v>-0.18</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.354900000000001</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.68</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5332</v>
+        <v>-0.3472</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.4628</v>
+        <v>-10.0688</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.141</v>
+        <v>1.0841</v>
       </c>
       <c r="J167" t="n">
-        <v>33.089</v>
+        <v>31.4389</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="J168" t="n">
-        <v>21.5586</v>
+        <v>20.9931</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5676</v>
+        <v>0.5522</v>
       </c>
       <c r="J169" t="n">
-        <v>16.4604</v>
+        <v>16.0138</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3311</v>
+        <v>-0.2618</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.601900000000001</v>
+        <v>-7.5922</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.732</v>
       </c>
       <c r="J171" t="n">
-        <v>-22.6113</v>
+        <v>-21.228</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.92</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0163</v>
+        <v>-0.0475</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.3749</v>
+        <v>-1.0925</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.66</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.4444</v>
+        <v>-0.328</v>
       </c>
       <c r="J173" t="n">
-        <v>-10.2212</v>
+        <v>-7.544</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.64</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4895</v>
+        <v>-0.3452</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.2585</v>
+        <v>-7.9396</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.55</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6293</v>
+        <v>-0.4281</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.4739</v>
+        <v>-9.846299999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6984</v>
+        <v>-0.475</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.0632</v>
+        <v>-10.925</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.87</v>
       </c>
       <c r="I177" t="n">
-        <v>1.8021</v>
+        <v>1.5327</v>
       </c>
       <c r="J177" t="n">
-        <v>41.4483</v>
+        <v>35.2521</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.61</v>
       </c>
       <c r="I178" t="n">
-        <v>1.3303</v>
+        <v>1.2311</v>
       </c>
       <c r="J178" t="n">
-        <v>30.5969</v>
+        <v>28.3153</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I179" t="n">
-        <v>1.02</v>
+        <v>1.0521</v>
       </c>
       <c r="J179" t="n">
-        <v>23.46</v>
+        <v>24.1983</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.5693</v>
+        <v>0.6813</v>
       </c>
       <c r="J180" t="n">
-        <v>13.0939</v>
+        <v>15.6699</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4181</v>
+        <v>-0.3343</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.616300000000001</v>
+        <v>-7.6889</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.83</v>
       </c>
       <c r="I182" t="n">
-        <v>1.6687</v>
+        <v>1.4578</v>
       </c>
       <c r="J182" t="n">
-        <v>30.0366</v>
+        <v>26.2404</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.81</v>
       </c>
       <c r="I183" t="n">
-        <v>1.6332</v>
+        <v>1.4356</v>
       </c>
       <c r="J183" t="n">
-        <v>29.3976</v>
+        <v>25.8408</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.48</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9593</v>
+        <v>1.0626</v>
       </c>
       <c r="J184" t="n">
-        <v>17.2674</v>
+        <v>19.1268</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.42</v>
       </c>
       <c r="I185" t="n">
-        <v>0.8363</v>
+        <v>0.9749</v>
       </c>
       <c r="J185" t="n">
-        <v>15.0534</v>
+        <v>17.5482</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.41</v>
       </c>
       <c r="I186" t="n">
-        <v>0.8158</v>
+        <v>0.9566</v>
       </c>
       <c r="J186" t="n">
-        <v>14.6844</v>
+        <v>17.2188</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.31</v>
+        <v>-0.2638</v>
       </c>
       <c r="J187" t="n">
-        <v>-5.58</v>
+        <v>-4.7484</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.66</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3557</v>
+        <v>-0.2961</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.4026</v>
+        <v>-5.3298</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.61</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4329</v>
+        <v>-0.348</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.7922</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.34</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.8714</v>
+        <v>-0.6035</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.6852</v>
+        <v>-10.863</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.32</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.898</v>
+        <v>-0.6233</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.164</v>
+        <v>-11.2194</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.55</v>
       </c>
       <c r="I192" t="n">
-        <v>1.3449</v>
+        <v>1.2186</v>
       </c>
       <c r="J192" t="n">
-        <v>40.347</v>
+        <v>36.558</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.385</v>
+        <v>0.4205</v>
       </c>
       <c r="J193" t="n">
-        <v>11.55</v>
+        <v>12.615</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.09</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2325</v>
+        <v>0.2852</v>
       </c>
       <c r="J194" t="n">
-        <v>6.975</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.07</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1704</v>
+        <v>0.2265</v>
       </c>
       <c r="J195" t="n">
-        <v>5.112</v>
+        <v>6.795</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4328</v>
+        <v>-0.3619</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.984</v>
+        <v>-10.857</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3647</v>
+        <v>0.4068</v>
       </c>
       <c r="J197" t="n">
-        <v>10.941</v>
+        <v>12.204</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.14</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3191</v>
+        <v>0.3481</v>
       </c>
       <c r="J198" t="n">
-        <v>9.573</v>
+        <v>10.443</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2709</v>
+        <v>-0.1694</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.127000000000001</v>
+        <v>-5.082</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3801</v>
+        <v>-0.2406</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.403</v>
+        <v>-7.218</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5196</v>
+        <v>-0.3375</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.588</v>
+        <v>-10.125</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7454</v>
+        <v>0.7081</v>
       </c>
       <c r="J202" t="n">
-        <v>26.8344</v>
+        <v>25.4916</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5808</v>
       </c>
       <c r="J203" t="n">
-        <v>22.374</v>
+        <v>20.9088</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3729</v>
+        <v>0.3378</v>
       </c>
       <c r="J204" t="n">
-        <v>13.4244</v>
+        <v>12.1608</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2573</v>
+        <v>-0.2062</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.2628</v>
+        <v>-7.4232</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.9379</v>
+        <v>-0.908</v>
       </c>
       <c r="J206" t="n">
-        <v>-33.7644</v>
+        <v>-32.688</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.3</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5043</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
-        <v>18.1548</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4646</v>
+        <v>0.5483</v>
       </c>
       <c r="J208" t="n">
-        <v>16.7256</v>
+        <v>19.7388</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.04</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0814</v>
+        <v>0.1095</v>
       </c>
       <c r="J209" t="n">
-        <v>2.9304</v>
+        <v>3.942</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3209</v>
+        <v>-0.1934</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.5524</v>
+        <v>-6.9624</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.78</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.422</v>
+        <v>-0.2643</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.192</v>
+        <v>-9.514799999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.65</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4941</v>
+        <v>1.3204</v>
       </c>
       <c r="J212" t="n">
-        <v>38.8466</v>
+        <v>34.3304</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.45</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1025</v>
+        <v>1.0693</v>
       </c>
       <c r="J213" t="n">
-        <v>28.665</v>
+        <v>27.8018</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.26</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6694</v>
+        <v>0.6933</v>
       </c>
       <c r="J214" t="n">
-        <v>17.4044</v>
+        <v>18.0258</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3033</v>
+        <v>0.3766</v>
       </c>
       <c r="J215" t="n">
-        <v>7.8858</v>
+        <v>9.791600000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9837</v>
+        <v>-0.9564</v>
       </c>
       <c r="J216" t="n">
-        <v>-25.5762</v>
+        <v>-24.8664</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.08</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2482</v>
+        <v>0.2504</v>
       </c>
       <c r="J217" t="n">
-        <v>6.4532</v>
+        <v>6.5104</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.88</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1869</v>
+        <v>-0.1419</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.8594</v>
+        <v>-3.6894</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.85</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2522</v>
+        <v>-0.1721</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.5572</v>
+        <v>-4.4746</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.85</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2522</v>
+        <v>-0.1721</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.5572</v>
+        <v>-4.4746</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5824</v>
+        <v>-0.3847</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.1424</v>
+        <v>-10.0022</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2100/event_2100_evp_summary.xlsx
+++ b/database/event/2100/event_2100_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.4177</v>
+        <v>3.2043</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5842</v>
+        <v>1.4853</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9049</v>
+        <v>0.8345</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4177</v>
+        <v>3.2043</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4177</v>
+        <v>3.2043</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1449</v>
+        <v>4.2882</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0703</v>
+        <v>4.8699</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5.0703</v>
+        <v>4.8699</v>
       </c>
       <c r="N2" t="n">
         <v>222</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.2526</v>
+        <v>3.1368</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5077</v>
+        <v>1.454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8304</v>
+        <v>0.8037</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2526</v>
+        <v>3.1368</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2526</v>
+        <v>3.1368</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7823</v>
+        <v>4.1405</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2214</v>
+        <v>5.0751</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2214</v>
+        <v>5.0751</v>
       </c>
       <c r="N3" t="n">
         <v>249</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2034</v>
+        <v>3.0202</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4849</v>
+        <v>1.3999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8082</v>
+        <v>0.7507</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2034</v>
+        <v>3.0202</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2034</v>
+        <v>3.0202</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6745</v>
+        <v>3.8852</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4948</v>
+        <v>4.4123</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4948</v>
+        <v>4.4123</v>
       </c>
       <c r="N4" t="n">
         <v>222</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0666</v>
+        <v>2.9155</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4215</v>
+        <v>1.3514</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7464</v>
+        <v>0.703</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0666</v>
+        <v>2.9155</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0666</v>
+        <v>2.9155</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3741</v>
+        <v>3.6561</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6578</v>
+        <v>4.4814</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6578</v>
+        <v>4.4814</v>
       </c>
       <c r="N5" t="n">
         <v>249</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.972</v>
+        <v>2.7436</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3776</v>
+        <v>1.2717</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7037</v>
+        <v>0.6247</v>
       </c>
       <c r="E6" t="n">
-        <v>2.972</v>
+        <v>2.7436</v>
       </c>
       <c r="F6" t="n">
-        <v>2.972</v>
+        <v>2.7436</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1662</v>
+        <v>3.2799</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5732</v>
+        <v>3.5401</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5732</v>
+        <v>3.5401</v>
       </c>
       <c r="N6" t="n">
         <v>165</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.562</v>
+        <v>2.4402</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1876</v>
+        <v>1.1311</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4866</v>
       </c>
       <c r="E7" t="n">
-        <v>2.562</v>
+        <v>2.4402</v>
       </c>
       <c r="F7" t="n">
-        <v>2.562</v>
+        <v>2.4402</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.562</v>
+        <v>2.6158</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7771</v>
+        <v>3.2063</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7771</v>
+        <v>3.2063</v>
       </c>
       <c r="N7" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3693</v>
+        <v>2.3929</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0982</v>
+        <v>1.1092</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4316</v>
+        <v>0.4651</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3693</v>
+        <v>2.3929</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3693</v>
+        <v>2.3929</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3693</v>
+        <v>2.5124</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2707</v>
+        <v>2.6435</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2707</v>
+        <v>2.6435</v>
       </c>
       <c r="N8" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1679</v>
+        <v>2.32</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0049</v>
+        <v>1.0754</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3407</v>
+        <v>0.4319</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1679</v>
+        <v>2.32</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1679</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1679</v>
+        <v>2.3528</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2571</v>
+        <v>2.4134</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2571</v>
+        <v>2.4134</v>
       </c>
       <c r="N9" t="n">
         <v>87</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1274</v>
+        <v>2.3108</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9861</v>
+        <v>1.0711</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3224</v>
+        <v>0.4277</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1274</v>
+        <v>2.3108</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1274</v>
+        <v>2.3108</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1274</v>
+        <v>2.3327</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9368</v>
+        <v>2.8593</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9368</v>
+        <v>2.8593</v>
       </c>
       <c r="N10" t="n">
         <v>249</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1019</v>
+        <v>2.1024</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9745</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3109</v>
+        <v>0.3329</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1019</v>
+        <v>2.1024</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1019</v>
+        <v>2.1024</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1019</v>
+        <v>2.1024</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3721</v>
+        <v>2.2692</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3721</v>
+        <v>2.2692</v>
       </c>
       <c r="N11" t="n">
         <v>156</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0244</v>
+        <v>2.0019</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9384</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2759</v>
+        <v>0.2871</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0244</v>
+        <v>2.0019</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0244</v>
+        <v>2.0019</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0244</v>
+        <v>2.0019</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2846</v>
+        <v>2.1607</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2846</v>
+        <v>2.1607</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7519</v>
+        <v>1.7938</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8121</v>
+        <v>0.8315</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1529</v>
+        <v>0.1924</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7519</v>
+        <v>1.7938</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7519</v>
+        <v>1.7938</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7519</v>
+        <v>1.7938</v>
       </c>
       <c r="I13" t="n">
-        <v>2.143</v>
+        <v>2.0371</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.143</v>
+        <v>2.0371</v>
       </c>
       <c r="N13" t="n">
         <v>222</v>
@@ -1044,32 +1044,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6939</v>
+        <v>1.677</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7852</v>
+        <v>0.7773</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1267</v>
+        <v>0.1392</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6939</v>
+        <v>1.677</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6939</v>
+        <v>1.677</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6939</v>
+        <v>1.677</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9116</v>
+        <v>1.81</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9116</v>
+        <v>1.81</v>
       </c>
       <c r="N14" t="n">
         <v>165</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6559</v>
+        <v>1.6746</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7762</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1095</v>
+        <v>0.1381</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6559</v>
+        <v>1.6746</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6559</v>
+        <v>1.6746</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6559</v>
+        <v>1.6746</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8687</v>
+        <v>1.8074</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8687</v>
+        <v>1.8074</v>
       </c>
       <c r="N15" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5859</v>
+        <v>1.6532</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7351</v>
+        <v>0.7663</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0779</v>
+        <v>0.1284</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5859</v>
+        <v>1.6532</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5859</v>
+        <v>1.6532</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5859</v>
+        <v>1.6532</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7897</v>
+        <v>1.7843</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7897</v>
+        <v>1.7843</v>
       </c>
       <c r="N16" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5459</v>
+        <v>1.599</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7166</v>
+        <v>0.7412</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0599</v>
+        <v>0.1037</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5459</v>
+        <v>1.599</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5459</v>
+        <v>1.599</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5459</v>
+        <v>1.599</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7446</v>
+        <v>1.7258</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7446</v>
+        <v>1.7258</v>
       </c>
       <c r="N17" t="n">
         <v>165</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.476</v>
+        <v>1.5106</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6842</v>
+        <v>0.7002</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0283</v>
+        <v>0.0635</v>
       </c>
       <c r="E18" t="n">
-        <v>1.476</v>
+        <v>1.5106</v>
       </c>
       <c r="F18" t="n">
-        <v>1.476</v>
+        <v>1.5106</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.476</v>
+        <v>1.5106</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6657</v>
+        <v>1.6304</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6657</v>
+        <v>1.6304</v>
       </c>
       <c r="N18" t="n">
         <v>156</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4421</v>
+        <v>1.4484</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6685</v>
+        <v>0.6714</v>
       </c>
       <c r="D19" t="n">
-        <v>0.013</v>
+        <v>0.0351</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4421</v>
+        <v>1.4484</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4421</v>
+        <v>1.4484</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4421</v>
+        <v>1.4484</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5632</v>
+        <v>1.524</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5632</v>
+        <v>1.524</v>
       </c>
       <c r="N19" t="n">
         <v>123</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2495</v>
+        <v>1.3175</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5792</v>
+        <v>0.6107</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0245</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2495</v>
+        <v>1.3175</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2495</v>
+        <v>1.3175</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2495</v>
+        <v>1.3175</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5284</v>
+        <v>1.4962</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5284</v>
+        <v>1.4962</v>
       </c>
       <c r="N20" t="n">
         <v>222</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1636</v>
+        <v>1.1485</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5394</v>
+        <v>0.5324</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1127</v>
+        <v>-0.1014</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1636</v>
+        <v>1.1485</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1636</v>
+        <v>1.1485</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1636</v>
+        <v>1.1485</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3132</v>
+        <v>1.2396</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3132</v>
+        <v>1.2396</v>
       </c>
       <c r="N21" t="n">
         <v>156</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0129</v>
+        <v>0.9649</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4695</v>
+        <v>0.4473</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1807</v>
+        <v>-0.185</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0129</v>
+        <v>0.9649</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0129</v>
+        <v>0.9649</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0129</v>
+        <v>0.9649</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0979</v>
+        <v>1.0153</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0979</v>
+        <v>1.0153</v>
       </c>
       <c r="N22" t="n">
         <v>123</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9605</v>
+        <v>0.9512</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4452</v>
+        <v>0.4409</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2044</v>
+        <v>-0.1912</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9605</v>
+        <v>0.9512</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9605</v>
+        <v>0.9512</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9605</v>
+        <v>0.9512</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0839</v>
+        <v>1.0266</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0839</v>
+        <v>1.0266</v>
       </c>
       <c r="N23" t="n">
         <v>165</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9256</v>
+        <v>0.948</v>
       </c>
       <c r="C24" t="n">
-        <v>0.429</v>
+        <v>0.4394</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2202</v>
+        <v>-0.1927</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9256</v>
+        <v>0.948</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9256</v>
+        <v>0.948</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9256</v>
+        <v>0.948</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0033</v>
+        <v>1.162</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0033</v>
+        <v>1.162</v>
       </c>
       <c r="N24" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8702</v>
+        <v>0.8848</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4034</v>
+        <v>0.4101</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2452</v>
+        <v>-0.2214</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8702</v>
+        <v>0.8848</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8702</v>
+        <v>0.8848</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8702</v>
+        <v>0.8848</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2013</v>
+        <v>0.931</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.2013</v>
+        <v>0.931</v>
       </c>
       <c r="N25" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8206</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3804</v>
+        <v>0.3591</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2676</v>
+        <v>-0.2715</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8206</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8206</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8206</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8544</v>
+        <v>0.7947</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8544</v>
+        <v>0.7947</v>
       </c>
       <c r="N26" t="n">
         <v>87</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6056</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2807</v>
+        <v>0.2628</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3646</v>
+        <v>-0.3661</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6056</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6056</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6056</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6056</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6056</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>79</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1017</v>
+        <v>0.1625</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0471</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5921</v>
+        <v>-0.5502</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1017</v>
+        <v>0.1625</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1017</v>
+        <v>0.1625</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1017</v>
+        <v>0.1625</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1059</v>
+        <v>0.1845</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>87</v>
+        <v>222</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1059</v>
+        <v>0.1845</v>
       </c>
       <c r="N28" t="n">
-        <v>87</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.066</v>
+        <v>0.0425</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0306</v>
+        <v>0.0197</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6082</v>
+        <v>-0.6049</v>
       </c>
       <c r="E29" t="n">
-        <v>0.066</v>
+        <v>0.0425</v>
       </c>
       <c r="F29" t="n">
-        <v>0.066</v>
+        <v>0.0425</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.066</v>
+        <v>0.0425</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0808</v>
+        <v>0.0436</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>222</v>
+        <v>87</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0808</v>
+        <v>0.0436</v>
       </c>
       <c r="N29" t="n">
-        <v>222</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0421</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0195</v>
+        <v>-0.0044</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.619</v>
+        <v>-0.6286</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0421</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0421</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0421</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0421</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0421</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EasTor</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0313</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0145</v>
+        <v>-0.0459</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6521</v>
+        <v>-0.6693</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0313</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0313</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0313</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0313</v>
+        <v>-0.1043</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0313</v>
+        <v>-0.1043</v>
       </c>
       <c r="N31" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>EasTor</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1324</v>
+        <v>-0.1335</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0614</v>
+        <v>-0.0619</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6978</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1324</v>
+        <v>-0.1335</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1324</v>
+        <v>-0.1335</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1324</v>
+        <v>-0.1335</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1435</v>
+        <v>-0.1335</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1435</v>
+        <v>-0.1335</v>
       </c>
       <c r="N32" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kairi</t>
+          <t>Hyper</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3715</v>
+        <v>-0.3897</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1722</v>
+        <v>-0.1806</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8057</v>
+        <v>-0.8016</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3715</v>
+        <v>-0.3897</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3715</v>
+        <v>-0.3897</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3715</v>
+        <v>-0.3897</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3715</v>
+        <v>-0.3997</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3715</v>
+        <v>-0.3997</v>
       </c>
       <c r="N33" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hyper</t>
+          <t>Kairi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.391</v>
+        <v>-0.4063</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1812</v>
+        <v>-0.1883</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8145</v>
+        <v>-0.8092</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.391</v>
+        <v>-0.4063</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.391</v>
+        <v>-0.4063</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.391</v>
+        <v>-0.4063</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4071</v>
+        <v>-0.4063</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4071</v>
+        <v>-0.4063</v>
       </c>
       <c r="N34" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.579</v>
+        <v>-0.632</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2684</v>
+        <v>-0.2929</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8994</v>
+        <v>-0.9119</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.579</v>
+        <v>-0.632</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.579</v>
+        <v>-0.632</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.579</v>
+        <v>-0.632</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6028</v>
+        <v>-0.6483</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6028</v>
+        <v>-0.6483</v>
       </c>
       <c r="N35" t="n">
         <v>87</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3166</v>
+        <v>-0.3417</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9464</v>
+        <v>-0.9597</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.7371</v>
       </c>
       <c r="N36" t="n">
         <v>79</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9991</v>
+        <v>-1.0673</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4631</v>
+        <v>-0.4947</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0891</v>
+        <v>-1.1101</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9991</v>
+        <v>-1.0673</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9991</v>
+        <v>-1.0673</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9991</v>
+        <v>-1.0673</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9991</v>
+        <v>-1.0673</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9991</v>
+        <v>-1.0673</v>
       </c>
       <c r="N37" t="n">
         <v>55</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1286</v>
+        <v>-1.1905</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5231</v>
+        <v>-0.5518</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1475</v>
+        <v>-1.1661</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1286</v>
+        <v>-1.1905</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1286</v>
+        <v>-1.1905</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1286</v>
+        <v>-1.1905</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1286</v>
+        <v>-1.1905</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1286</v>
+        <v>-1.1905</v>
       </c>
       <c r="N38" t="n">
         <v>55</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1591</v>
+        <v>-1.1952</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5373</v>
+        <v>-0.554</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1613</v>
+        <v>-1.1683</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1591</v>
+        <v>-1.1952</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1591</v>
+        <v>-1.1952</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1591</v>
+        <v>-1.1952</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1591</v>
+        <v>-1.1952</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1591</v>
+        <v>-1.1952</v>
       </c>
       <c r="N39" t="n">
         <v>79</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2963</v>
+        <v>-1.3425</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6009</v>
+        <v>-0.6223</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2232</v>
+        <v>-1.2353</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2963</v>
+        <v>-1.3425</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2963</v>
+        <v>-1.3425</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2963</v>
+        <v>-1.3425</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2963</v>
+        <v>-1.3425</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2963</v>
+        <v>-1.3425</v>
       </c>
       <c r="N40" t="n">
         <v>55</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8741</v>
+        <v>-1.8833</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8687</v>
+        <v>-0.873</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4841</v>
+        <v>-1.4815</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8741</v>
+        <v>-1.8833</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8741</v>
+        <v>-1.8833</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8741</v>
+        <v>-1.8833</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8741</v>
+        <v>-1.8833</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8741</v>
+        <v>-1.8833</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2429,10 +2429,10 @@
         <v>1.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2098</v>
+        <v>0.2159</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0842</v>
+        <v>6.2611</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0956</v>
+        <v>0.1027</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7724</v>
+        <v>2.9783</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0614</v>
+        <v>-0.0711</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.7806</v>
+        <v>-2.0619</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.074</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.146</v>
+        <v>-2.4534</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1539</v>
+        <v>-0.1675</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.4631</v>
+        <v>-4.8575</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2045</v>
+        <v>1.1695</v>
       </c>
       <c r="J7" t="n">
-        <v>34.9305</v>
+        <v>33.9155</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0173</v>
+        <v>0.9597</v>
       </c>
       <c r="J8" t="n">
-        <v>29.5017</v>
+        <v>27.8313</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0374</v>
+        <v>-0.0257</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0846</v>
+        <v>-0.7453</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2057</v>
+        <v>-0.1975</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.9653</v>
+        <v>-5.7275</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4493</v>
+        <v>-0.4245</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.0297</v>
+        <v>-12.3105</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9303</v>
+        <v>0.8777</v>
       </c>
       <c r="J12" t="n">
-        <v>27.909</v>
+        <v>26.331</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1206</v>
+        <v>0.1278</v>
       </c>
       <c r="J13" t="n">
-        <v>3.618</v>
+        <v>3.834</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0613</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.839</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.276</v>
+        <v>-0.2894</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.682</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3807</v>
+        <v>-0.3911</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.421</v>
+        <v>-11.733</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8181</v>
+        <v>0.7659</v>
       </c>
       <c r="J17" t="n">
-        <v>24.543</v>
+        <v>22.977</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4919</v>
+        <v>0.4768</v>
       </c>
       <c r="J18" t="n">
-        <v>14.757</v>
+        <v>14.304</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1179</v>
+        <v>0.1273</v>
       </c>
       <c r="J19" t="n">
-        <v>3.537</v>
+        <v>3.819</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3082</v>
+        <v>-0.3002</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.246</v>
+        <v>-9.006</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3082</v>
+        <v>-0.3002</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.246</v>
+        <v>-9.006</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2395</v>
+        <v>1.2143</v>
       </c>
       <c r="J22" t="n">
-        <v>29.748</v>
+        <v>29.1432</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0541</v>
+        <v>1.0106</v>
       </c>
       <c r="J23" t="n">
-        <v>25.2984</v>
+        <v>24.2544</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.35</v>
       </c>
       <c r="I24" t="n">
-        <v>0.878</v>
+        <v>0.8324</v>
       </c>
       <c r="J24" t="n">
-        <v>21.072</v>
+        <v>19.9776</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.32</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8137</v>
+        <v>0.7756</v>
       </c>
       <c r="J25" t="n">
-        <v>19.5288</v>
+        <v>18.6144</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4769</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.3744</v>
+        <v>-11.4456</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.24</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6337</v>
+        <v>0.5913</v>
       </c>
       <c r="J27" t="n">
-        <v>15.2088</v>
+        <v>14.1912</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.79</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2215</v>
+        <v>-0.2411</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.316</v>
+        <v>-5.7864</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2311</v>
+        <v>-0.2506</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.5464</v>
+        <v>-6.0144</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4461</v>
+        <v>-0.458</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.7064</v>
+        <v>-10.992</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5294</v>
+        <v>-0.5363</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.7056</v>
+        <v>-12.8712</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2966</v>
+        <v>1.2757</v>
       </c>
       <c r="J32" t="n">
-        <v>29.8218</v>
+        <v>29.3411</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.56</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1876</v>
+        <v>1.1593</v>
       </c>
       <c r="J33" t="n">
-        <v>27.3148</v>
+        <v>26.6639</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6775</v>
+        <v>0.6553</v>
       </c>
       <c r="J34" t="n">
-        <v>15.5825</v>
+        <v>15.0719</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.24</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6307</v>
+        <v>0.6137</v>
       </c>
       <c r="J35" t="n">
-        <v>14.5061</v>
+        <v>14.1151</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2488</v>
+        <v>-0.2276</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.7224</v>
+        <v>-5.2348</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.99</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0437</v>
+        <v>0.0159</v>
       </c>
       <c r="J37" t="n">
-        <v>1.0051</v>
+        <v>0.3657</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2086</v>
+        <v>-0.229</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.7978</v>
+        <v>-5.267</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.68</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3213</v>
+        <v>-0.3395</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.3899</v>
+        <v>-7.8085</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3588</v>
+        <v>-0.3756</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.2524</v>
+        <v>-8.6388</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3869</v>
+        <v>-0.4024</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.8987</v>
+        <v>-9.2552</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.09</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2304</v>
+        <v>0.236</v>
       </c>
       <c r="J42" t="n">
-        <v>6.4512</v>
+        <v>6.608</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0405</v>
+        <v>0.0453</v>
       </c>
       <c r="J43" t="n">
-        <v>1.134</v>
+        <v>1.2684</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0195</v>
+        <v>-0.0245</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.546</v>
+        <v>-0.6860000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0982</v>
+        <v>-0.1101</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.7496</v>
+        <v>-3.0828</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1432</v>
+        <v>-0.1567</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.0096</v>
+        <v>-4.3876</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.97</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7213</v>
+        <v>1.7149</v>
       </c>
       <c r="J47" t="n">
-        <v>48.1964</v>
+        <v>48.0172</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8862</v>
+        <v>0.8339</v>
       </c>
       <c r="J48" t="n">
-        <v>24.8136</v>
+        <v>23.3492</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2159</v>
+        <v>0.2293</v>
       </c>
       <c r="J49" t="n">
-        <v>6.0452</v>
+        <v>6.4204</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6221</v>
+        <v>-0.5783</v>
       </c>
       <c r="J50" t="n">
-        <v>-17.4188</v>
+        <v>-16.1924</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7254</v>
+        <v>-0.6701</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.3112</v>
+        <v>-18.7628</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8105</v>
+        <v>0.769</v>
       </c>
       <c r="J52" t="n">
-        <v>21.8835</v>
+        <v>20.763</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7877</v>
+        <v>0.749</v>
       </c>
       <c r="J53" t="n">
-        <v>21.2679</v>
+        <v>20.223</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.719</v>
+        <v>0.6883</v>
       </c>
       <c r="J54" t="n">
-        <v>19.413</v>
+        <v>18.5841</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.16</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4581</v>
+        <v>0.4537</v>
       </c>
       <c r="J55" t="n">
-        <v>12.3687</v>
+        <v>12.2499</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.07</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2096</v>
+        <v>0.225</v>
       </c>
       <c r="J56" t="n">
-        <v>5.6592</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2024</v>
+        <v>0.1998</v>
       </c>
       <c r="J57" t="n">
-        <v>5.4648</v>
+        <v>5.3946</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0487</v>
+        <v>-0.0614</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.3149</v>
+        <v>-1.6578</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2125</v>
+        <v>-0.2297</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.7375</v>
+        <v>-6.2019</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2616</v>
+        <v>-0.2782</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.0632</v>
+        <v>-7.5114</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2907</v>
+        <v>-0.3066</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.8489</v>
+        <v>-8.2782</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.63</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2634</v>
+        <v>1.2421</v>
       </c>
       <c r="J62" t="n">
-        <v>29.0582</v>
+        <v>28.5683</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0825</v>
+        <v>1.0463</v>
       </c>
       <c r="J63" t="n">
-        <v>24.8975</v>
+        <v>24.0649</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.48</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0825</v>
+        <v>1.0463</v>
       </c>
       <c r="J64" t="n">
-        <v>24.8975</v>
+        <v>24.0649</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7822</v>
+        <v>0.7498</v>
       </c>
       <c r="J65" t="n">
-        <v>17.9906</v>
+        <v>17.2454</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0907</v>
+        <v>-0.063</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.0861</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.31</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8259</v>
+        <v>0.7553</v>
       </c>
       <c r="J67" t="n">
-        <v>18.9957</v>
+        <v>17.3719</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2413</v>
+        <v>-0.2626</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.5499</v>
+        <v>-6.0398</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.62</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3709</v>
+        <v>-0.3883</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.5307</v>
+        <v>-8.930899999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.46</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5205</v>
+        <v>-0.5292</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.9715</v>
+        <v>-12.1716</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.36</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6137</v>
+        <v>-0.6158</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.1151</v>
+        <v>-14.1634</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4353</v>
+        <v>0.4202</v>
       </c>
       <c r="J72" t="n">
-        <v>12.6237</v>
+        <v>12.1858</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0618</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.7922</v>
+        <v>-2.1837</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0886</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.1576</v>
+        <v>-2.5694</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.66</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3573</v>
+        <v>-0.3711</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.3617</v>
+        <v>-10.7619</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4135</v>
+        <v>-0.4248</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.9915</v>
+        <v>-12.3192</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2216</v>
+        <v>1.1916</v>
       </c>
       <c r="J77" t="n">
-        <v>35.4264</v>
+        <v>34.5564</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5198</v>
       </c>
       <c r="J78" t="n">
-        <v>15.3903</v>
+        <v>15.0742</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5198</v>
       </c>
       <c r="J79" t="n">
-        <v>15.3903</v>
+        <v>15.0742</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4809</v>
+        <v>0.4749</v>
       </c>
       <c r="J80" t="n">
-        <v>13.9461</v>
+        <v>13.7721</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.05</v>
       </c>
       <c r="I81" t="n">
-        <v>0.144</v>
+        <v>0.1637</v>
       </c>
       <c r="J81" t="n">
-        <v>4.176</v>
+        <v>4.7473</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.78</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4384</v>
+        <v>1.4281</v>
       </c>
       <c r="J82" t="n">
-        <v>30.2064</v>
+        <v>29.9901</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.62</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2501</v>
+        <v>1.2281</v>
       </c>
       <c r="J83" t="n">
-        <v>26.2521</v>
+        <v>25.7901</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9173</v>
       </c>
       <c r="J84" t="n">
-        <v>20.3112</v>
+        <v>19.2633</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.09</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2306</v>
+        <v>0.2535</v>
       </c>
       <c r="J85" t="n">
-        <v>4.8426</v>
+        <v>5.3235</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1085</v>
+        <v>0.1388</v>
       </c>
       <c r="J86" t="n">
-        <v>2.2785</v>
+        <v>2.9148</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.23</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6308</v>
+        <v>0.5859</v>
       </c>
       <c r="J87" t="n">
-        <v>13.2468</v>
+        <v>12.3039</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0222</v>
+        <v>-0.0407</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.4662</v>
+        <v>-0.8547</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.396</v>
+        <v>-0.4111</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.633100000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.53</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4614</v>
+        <v>-0.4729</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.689399999999999</v>
+        <v>-9.930899999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5911</v>
+        <v>-0.5941</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.4131</v>
+        <v>-12.4761</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.01</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0639</v>
       </c>
       <c r="J92" t="n">
-        <v>1.655</v>
+        <v>1.5975</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0069</v>
+        <v>-0.0148</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.1725</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.97</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0376</v>
+        <v>-0.0487</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.2175</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2831</v>
+        <v>-0.2988</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.0775</v>
+        <v>-7.47</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3311</v>
+        <v>-0.3454</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.2775</v>
+        <v>-8.635</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.68</v>
       </c>
       <c r="I97" t="n">
-        <v>1.348</v>
+        <v>1.3276</v>
       </c>
       <c r="J97" t="n">
-        <v>33.7</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.64</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2993</v>
+        <v>1.2759</v>
       </c>
       <c r="J98" t="n">
-        <v>32.4825</v>
+        <v>31.8975</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0674</v>
+        <v>0.0922</v>
       </c>
       <c r="J99" t="n">
-        <v>1.685</v>
+        <v>2.305</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.02</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0302</v>
+        <v>0.0557</v>
       </c>
       <c r="J100" t="n">
-        <v>0.755</v>
+        <v>1.3925</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1619</v>
+        <v>-0.1469</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.0475</v>
+        <v>-3.6725</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.19</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5676</v>
+        <v>0.5451</v>
       </c>
       <c r="J102" t="n">
-        <v>20.4336</v>
+        <v>19.6236</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5676</v>
+        <v>0.5451</v>
       </c>
       <c r="J103" t="n">
-        <v>20.4336</v>
+        <v>19.6236</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4105</v>
+        <v>0.4033</v>
       </c>
       <c r="J104" t="n">
-        <v>14.778</v>
+        <v>14.5188</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1828</v>
+        <v>-0.1815</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.5808</v>
+        <v>-6.534</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.88</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.426</v>
+        <v>-0.4081</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.336</v>
+        <v>-14.6916</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6449</v>
       </c>
       <c r="J107" t="n">
-        <v>23.9688</v>
+        <v>23.2164</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3866</v>
+        <v>0.3883</v>
       </c>
       <c r="J108" t="n">
-        <v>13.9176</v>
+        <v>13.9788</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.03</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0848</v>
+        <v>0.0951</v>
       </c>
       <c r="J109" t="n">
-        <v>3.0528</v>
+        <v>3.4236</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1622</v>
+        <v>-0.174</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.8392</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.84</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2045</v>
+        <v>-0.2167</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.362</v>
+        <v>-7.8012</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.69</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3772</v>
+        <v>1.3555</v>
       </c>
       <c r="J112" t="n">
-        <v>34.43</v>
+        <v>33.8875</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.27</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7217</v>
+        <v>0.6901</v>
       </c>
       <c r="J113" t="n">
-        <v>18.0425</v>
+        <v>17.2525</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2125</v>
+        <v>0.227</v>
       </c>
       <c r="J114" t="n">
-        <v>5.3125</v>
+        <v>5.675</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1817</v>
+        <v>0.198</v>
       </c>
       <c r="J115" t="n">
-        <v>4.5425</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.96</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2195</v>
+        <v>-0.2071</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.4875</v>
+        <v>-5.1775</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3476</v>
+        <v>0.3399</v>
       </c>
       <c r="J117" t="n">
-        <v>8.69</v>
+        <v>8.4975</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2416</v>
+        <v>0.2391</v>
       </c>
       <c r="J118" t="n">
-        <v>6.04</v>
+        <v>5.9775</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="J119" t="n">
-        <v>2.4</v>
+        <v>2.375</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.75</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2735</v>
+        <v>-0.2893</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.8375</v>
+        <v>-7.2325</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.42</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5793</v>
+        <v>-0.581</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.4825</v>
+        <v>-14.525</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.88</v>
       </c>
       <c r="I122" t="n">
-        <v>1.522</v>
+        <v>1.5215</v>
       </c>
       <c r="J122" t="n">
-        <v>30.44</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.58</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1826</v>
+        <v>1.1598</v>
       </c>
       <c r="J123" t="n">
-        <v>23.652</v>
+        <v>23.196</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.53</v>
       </c>
       <c r="I124" t="n">
-        <v>1.1261</v>
+        <v>1.0984</v>
       </c>
       <c r="J124" t="n">
-        <v>22.522</v>
+        <v>21.968</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.47</v>
       </c>
       <c r="I125" t="n">
-        <v>1.0555</v>
+        <v>1.0183</v>
       </c>
       <c r="J125" t="n">
-        <v>21.11</v>
+        <v>20.366</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.23</v>
       </c>
       <c r="I126" t="n">
-        <v>0.5649</v>
+        <v>0.5632</v>
       </c>
       <c r="J126" t="n">
-        <v>11.298</v>
+        <v>11.264</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.8</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.1909</v>
+        <v>-0.2152</v>
       </c>
       <c r="J127" t="n">
-        <v>-3.818</v>
+        <v>-4.304</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2226</v>
+        <v>-0.2461</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.452</v>
+        <v>-4.922</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2925</v>
+        <v>-0.3137</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.85</v>
+        <v>-6.274</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3829</v>
+        <v>-0.4009</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.658</v>
+        <v>-8.018000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.5416</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.656</v>
+        <v>-10.832</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.72</v>
       </c>
       <c r="I132" t="n">
-        <v>1.343</v>
+        <v>1.3318</v>
       </c>
       <c r="J132" t="n">
-        <v>25.517</v>
+        <v>25.3042</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.66</v>
       </c>
       <c r="I133" t="n">
-        <v>1.2747</v>
+        <v>1.2588</v>
       </c>
       <c r="J133" t="n">
-        <v>24.2193</v>
+        <v>23.9172</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0683</v>
+        <v>1.0333</v>
       </c>
       <c r="J134" t="n">
-        <v>20.2977</v>
+        <v>19.6327</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.46</v>
       </c>
       <c r="I135" t="n">
-        <v>1.0434</v>
+        <v>1.0038</v>
       </c>
       <c r="J135" t="n">
-        <v>19.8246</v>
+        <v>19.0722</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.34</v>
       </c>
       <c r="I136" t="n">
-        <v>0.8196</v>
+        <v>0.7881</v>
       </c>
       <c r="J136" t="n">
-        <v>15.5724</v>
+        <v>14.9739</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1881</v>
+        <v>-0.2151</v>
       </c>
       <c r="J137" t="n">
-        <v>-3.5739</v>
+        <v>-4.0869</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.75</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2313</v>
+        <v>-0.2568</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.3947</v>
+        <v>-4.8792</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.55</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4212</v>
+        <v>-0.4386</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.002800000000001</v>
+        <v>-8.333399999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.54</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4305</v>
+        <v>-0.4473</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.179500000000001</v>
+        <v>-8.498699999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5153</v>
+        <v>-0.5265</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.790699999999999</v>
+        <v>-10.0035</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4508</v>
+        <v>1.4331</v>
       </c>
       <c r="J142" t="n">
-        <v>42.0732</v>
+        <v>41.5599</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.3</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7511</v>
       </c>
       <c r="J143" t="n">
-        <v>22.9332</v>
+        <v>21.7819</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.435</v>
+        <v>0.4321</v>
       </c>
       <c r="J144" t="n">
-        <v>12.615</v>
+        <v>12.5309</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.03</v>
       </c>
       <c r="I145" t="n">
-        <v>0.082</v>
+        <v>0.1024</v>
       </c>
       <c r="J145" t="n">
-        <v>2.378</v>
+        <v>2.9696</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.5806</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.1395</v>
+        <v>-16.8374</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.22</v>
       </c>
       <c r="I147" t="n">
-        <v>0.504</v>
+        <v>0.4887</v>
       </c>
       <c r="J147" t="n">
-        <v>14.616</v>
+        <v>14.1723</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.16</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3897</v>
+        <v>0.3829</v>
       </c>
       <c r="J148" t="n">
-        <v>11.3013</v>
+        <v>11.1041</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2198</v>
+        <v>-0.2353</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.3742</v>
+        <v>-6.8237</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.74</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2888</v>
+        <v>-0.3032</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.3752</v>
+        <v>-8.7928</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3367</v>
+        <v>-0.3498</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.7643</v>
+        <v>-10.1442</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.33</v>
       </c>
       <c r="I152" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J152" t="n">
-        <v>33.0084</v>
+        <v>34.8696</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.64</v>
       </c>
       <c r="I153" t="n">
-        <v>1.248</v>
+        <v>1.231</v>
       </c>
       <c r="J153" t="n">
-        <v>22.464</v>
+        <v>22.158</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.54</v>
       </c>
       <c r="I154" t="n">
-        <v>1.1355</v>
+        <v>1.1092</v>
       </c>
       <c r="J154" t="n">
-        <v>20.439</v>
+        <v>19.9656</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.25</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6071</v>
+        <v>0.6018</v>
       </c>
       <c r="J155" t="n">
-        <v>10.9278</v>
+        <v>10.8324</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1355</v>
+        <v>0.1731</v>
       </c>
       <c r="J156" t="n">
-        <v>2.439</v>
+        <v>3.1158</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4529</v>
+        <v>0.4052</v>
       </c>
       <c r="J157" t="n">
-        <v>8.152200000000001</v>
+        <v>7.2936</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.68</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3048</v>
+        <v>-0.3269</v>
       </c>
       <c r="J158" t="n">
-        <v>-5.4864</v>
+        <v>-5.8842</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3594</v>
+        <v>-0.3795</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.4692</v>
+        <v>-6.831</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.53</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4417</v>
+        <v>-0.4575</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.9506</v>
+        <v>-8.234999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.2</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7553</v>
+        <v>-0.7467</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.5954</v>
+        <v>-13.4406</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.09</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2449</v>
+        <v>0.2466</v>
       </c>
       <c r="J162" t="n">
-        <v>7.1021</v>
+        <v>7.1514</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1791</v>
+        <v>0.1827</v>
       </c>
       <c r="J163" t="n">
-        <v>5.1939</v>
+        <v>5.2983</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.98</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0303</v>
+        <v>-0.0384</v>
       </c>
       <c r="J164" t="n">
-        <v>-0.8787</v>
+        <v>-1.1136</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.18</v>
+        <v>-0.1953</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.22</v>
+        <v>-5.6637</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.68</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3472</v>
+        <v>-0.3597</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.0688</v>
+        <v>-10.4313</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0841</v>
+        <v>1.0367</v>
       </c>
       <c r="J167" t="n">
-        <v>31.4389</v>
+        <v>30.0643</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.7239</v>
+        <v>0.6871</v>
       </c>
       <c r="J168" t="n">
-        <v>20.9931</v>
+        <v>19.9259</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5522</v>
+        <v>0.5345</v>
       </c>
       <c r="J169" t="n">
-        <v>16.0138</v>
+        <v>15.5005</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2618</v>
+        <v>-0.2532</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.5922</v>
+        <v>-7.3428</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.732</v>
+        <v>-0.6793</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.228</v>
+        <v>-19.6997</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.92</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0475</v>
+        <v>-0.0737</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.0925</v>
+        <v>-1.6951</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.66</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.328</v>
+        <v>-0.3484</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.544</v>
+        <v>-8.013199999999999</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.64</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3452</v>
+        <v>-0.3651</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.9396</v>
+        <v>-8.3973</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.55</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4281</v>
+        <v>-0.4439</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.846299999999999</v>
+        <v>-10.2097</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.475</v>
+        <v>-0.4879</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.925</v>
+        <v>-11.2217</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.87</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5327</v>
+        <v>1.529</v>
       </c>
       <c r="J177" t="n">
-        <v>35.2521</v>
+        <v>35.167</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.61</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2311</v>
+        <v>1.2092</v>
       </c>
       <c r="J178" t="n">
-        <v>28.3153</v>
+        <v>27.8116</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I179" t="n">
-        <v>1.0521</v>
+        <v>1.0118</v>
       </c>
       <c r="J179" t="n">
-        <v>24.1983</v>
+        <v>23.2714</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6813</v>
+        <v>0.6624</v>
       </c>
       <c r="J180" t="n">
-        <v>15.6699</v>
+        <v>15.2352</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3343</v>
+        <v>-0.3041</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.6889</v>
+        <v>-6.9943</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.83</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4578</v>
+        <v>1.4553</v>
       </c>
       <c r="J182" t="n">
-        <v>26.2404</v>
+        <v>26.1954</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.81</v>
       </c>
       <c r="I183" t="n">
-        <v>1.4356</v>
+        <v>1.4318</v>
       </c>
       <c r="J183" t="n">
-        <v>25.8408</v>
+        <v>25.7724</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.48</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0626</v>
+        <v>1.0279</v>
       </c>
       <c r="J184" t="n">
-        <v>19.1268</v>
+        <v>18.5022</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.42</v>
       </c>
       <c r="I185" t="n">
-        <v>0.9749</v>
+        <v>0.931</v>
       </c>
       <c r="J185" t="n">
-        <v>17.5482</v>
+        <v>16.758</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.41</v>
       </c>
       <c r="I186" t="n">
-        <v>0.9566</v>
+        <v>0.913</v>
       </c>
       <c r="J186" t="n">
-        <v>17.2188</v>
+        <v>16.434</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2638</v>
+        <v>-0.2931</v>
       </c>
       <c r="J187" t="n">
-        <v>-4.7484</v>
+        <v>-5.2758</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.66</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2961</v>
+        <v>-0.3236</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.3298</v>
+        <v>-5.8248</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.61</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.348</v>
+        <v>-0.3724</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.264</v>
+        <v>-6.7032</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.34</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6035</v>
+        <v>-0.6101</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.863</v>
+        <v>-10.9818</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.32</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6233</v>
+        <v>-0.6282</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2194</v>
+        <v>-11.3076</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.55</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2186</v>
+        <v>1.1843</v>
       </c>
       <c r="J192" t="n">
-        <v>36.558</v>
+        <v>35.529</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4205</v>
+        <v>0.4163</v>
       </c>
       <c r="J193" t="n">
-        <v>12.615</v>
+        <v>12.489</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.09</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2852</v>
+        <v>0.2915</v>
       </c>
       <c r="J194" t="n">
-        <v>8.555999999999999</v>
+        <v>8.744999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.07</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2265</v>
+        <v>0.2367</v>
       </c>
       <c r="J195" t="n">
-        <v>6.795</v>
+        <v>7.101</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3619</v>
+        <v>-0.3445</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.857</v>
+        <v>-10.335</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4068</v>
+        <v>0.3993</v>
       </c>
       <c r="J197" t="n">
-        <v>12.204</v>
+        <v>11.979</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.14</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3481</v>
+        <v>0.3444</v>
       </c>
       <c r="J198" t="n">
-        <v>10.443</v>
+        <v>10.332</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1694</v>
+        <v>-0.1846</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.082</v>
+        <v>-5.538</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2406</v>
+        <v>-0.2557</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.218</v>
+        <v>-7.671</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3375</v>
+        <v>-0.3504</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.125</v>
+        <v>-10.512</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7081</v>
+        <v>0.6671</v>
       </c>
       <c r="J202" t="n">
-        <v>25.4916</v>
+        <v>24.0156</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5808</v>
+        <v>0.5543</v>
       </c>
       <c r="J203" t="n">
-        <v>20.9088</v>
+        <v>19.9548</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3378</v>
+        <v>0.3343</v>
       </c>
       <c r="J204" t="n">
-        <v>12.1608</v>
+        <v>12.0348</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2062</v>
+        <v>-0.2065</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.4232</v>
+        <v>-7.434</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.908</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>-32.688</v>
+        <v>-30.1392</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.3</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>0.5848</v>
       </c>
       <c r="J207" t="n">
-        <v>21.6</v>
+        <v>21.0528</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5483</v>
+        <v>0.5376</v>
       </c>
       <c r="J208" t="n">
-        <v>19.7388</v>
+        <v>19.3536</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.04</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1095</v>
+        <v>0.12</v>
       </c>
       <c r="J209" t="n">
-        <v>3.942</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1934</v>
+        <v>-0.2057</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.9624</v>
+        <v>-7.4052</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.78</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2643</v>
+        <v>-0.2763</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.514799999999999</v>
+        <v>-9.9468</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.65</v>
       </c>
       <c r="I212" t="n">
-        <v>1.3204</v>
+        <v>1.2968</v>
       </c>
       <c r="J212" t="n">
-        <v>34.3304</v>
+        <v>33.7168</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.45</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0693</v>
+        <v>1.0252</v>
       </c>
       <c r="J213" t="n">
-        <v>27.8018</v>
+        <v>26.6552</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.26</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6933</v>
+        <v>0.666</v>
       </c>
       <c r="J214" t="n">
-        <v>18.0258</v>
+        <v>17.316</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3766</v>
+        <v>0.3802</v>
       </c>
       <c r="J215" t="n">
-        <v>9.791600000000001</v>
+        <v>9.885199999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.9564</v>
+        <v>-0.8714</v>
       </c>
       <c r="J216" t="n">
-        <v>-24.8664</v>
+        <v>-22.6564</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.08</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2504</v>
+        <v>0.2456</v>
       </c>
       <c r="J217" t="n">
-        <v>6.5104</v>
+        <v>6.3856</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.88</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1419</v>
+        <v>-0.1584</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.6894</v>
+        <v>-4.1184</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.85</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1721</v>
+        <v>-0.1892</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.4746</v>
+        <v>-4.9192</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.85</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1721</v>
+        <v>-0.1892</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.4746</v>
+        <v>-4.9192</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3847</v>
+        <v>-0.3975</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.0022</v>
+        <v>-10.335</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2100/event_2100_evp_summary.xlsx
+++ b/database/event/2100/event_2100_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.2043</v>
+        <v>3.088</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4853</v>
+        <v>1.4314</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8345</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2043</v>
+        <v>3.088</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2043</v>
+        <v>3.088</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2882</v>
+        <v>4.1267</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8699</v>
+        <v>4.7083</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8699</v>
+        <v>4.7083</v>
       </c>
       <c r="N2" t="n">
         <v>222</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.1368</v>
+        <v>3.0321</v>
       </c>
       <c r="C3" t="n">
-        <v>1.454</v>
+        <v>1.4055</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8037</v>
+        <v>0.7755</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1368</v>
+        <v>3.0321</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1368</v>
+        <v>3.0321</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1405</v>
+        <v>3.9985</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0751</v>
+        <v>4.9377</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0751</v>
+        <v>4.9377</v>
       </c>
       <c r="N3" t="n">
         <v>249</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0202</v>
+        <v>2.9999</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3999</v>
+        <v>1.3905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7507</v>
+        <v>0.7608</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0202</v>
+        <v>2.9999</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0202</v>
+        <v>2.9999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8852</v>
+        <v>3.9247</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4123</v>
+        <v>4.4779</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4123</v>
+        <v>4.4779</v>
       </c>
       <c r="N4" t="n">
         <v>222</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9155</v>
+        <v>2.8828</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3514</v>
+        <v>1.3363</v>
       </c>
       <c r="D5" t="n">
-        <v>0.703</v>
+        <v>0.7075</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9155</v>
+        <v>2.8828</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9155</v>
+        <v>2.8828</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6561</v>
+        <v>3.6564</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4814</v>
+        <v>4.5152</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4814</v>
+        <v>4.5152</v>
       </c>
       <c r="N5" t="n">
         <v>249</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.7436</v>
+        <v>2.6894</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2717</v>
+        <v>1.2466</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6247</v>
+        <v>0.6194</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7436</v>
+        <v>2.6894</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7436</v>
+        <v>2.6894</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2799</v>
+        <v>3.2133</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5401</v>
+        <v>3.4778</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5401</v>
+        <v>3.4778</v>
       </c>
       <c r="N6" t="n">
         <v>165</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4402</v>
+        <v>2.4421</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1311</v>
+        <v>1.132</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4866</v>
+        <v>0.5067</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4402</v>
+        <v>2.4421</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4402</v>
+        <v>2.4421</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6158</v>
+        <v>2.6463</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2063</v>
+        <v>3.2679</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2063</v>
+        <v>3.2679</v>
       </c>
       <c r="N7" t="n">
         <v>249</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3929</v>
+        <v>2.4017</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1092</v>
+        <v>1.1133</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4651</v>
+        <v>0.4883</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3929</v>
+        <v>2.4017</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3929</v>
+        <v>2.4017</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5124</v>
+        <v>2.5538</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6435</v>
+        <v>2.6921</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6435</v>
+        <v>2.6921</v>
       </c>
       <c r="N8" t="n">
         <v>123</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.32</v>
+        <v>2.3004</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0754</v>
+        <v>1.0663</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4319</v>
+        <v>0.4422</v>
       </c>
       <c r="E9" t="n">
-        <v>2.32</v>
+        <v>2.3004</v>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>2.3004</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3528</v>
+        <v>2.3216</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4134</v>
+        <v>2.3837</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4134</v>
+        <v>2.3837</v>
       </c>
       <c r="N9" t="n">
         <v>87</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3108</v>
+        <v>2.2529</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0711</v>
+        <v>1.0443</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4277</v>
+        <v>0.4205</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3108</v>
+        <v>2.2529</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3108</v>
+        <v>2.2529</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3327</v>
+        <v>2.2529</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8593</v>
+        <v>2.7821</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8593</v>
+        <v>2.7821</v>
       </c>
       <c r="N10" t="n">
         <v>249</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1024</v>
+        <v>2.0591</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9745</v>
+        <v>0.9545</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3329</v>
+        <v>0.3322</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1024</v>
+        <v>2.0591</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1024</v>
+        <v>2.0591</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1024</v>
+        <v>2.0591</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2692</v>
+        <v>2.2287</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2692</v>
+        <v>2.2287</v>
       </c>
       <c r="N11" t="n">
         <v>156</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0019</v>
+        <v>2.0292</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9406</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2871</v>
+        <v>0.3186</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0019</v>
+        <v>2.0292</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0019</v>
+        <v>2.0292</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0019</v>
+        <v>2.0292</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1607</v>
+        <v>2.1963</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1607</v>
+        <v>2.1963</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7938</v>
+        <v>1.8215</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8315</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1924</v>
+        <v>0.224</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7938</v>
+        <v>1.8215</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7938</v>
+        <v>1.8215</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7938</v>
+        <v>1.8215</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0371</v>
+        <v>2.0782</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.0371</v>
+        <v>2.0782</v>
       </c>
       <c r="N13" t="n">
         <v>222</v>
@@ -1044,32 +1044,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.677</v>
+        <v>1.6635</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7773</v>
+        <v>0.7711</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1392</v>
+        <v>0.152</v>
       </c>
       <c r="E14" t="n">
-        <v>1.677</v>
+        <v>1.6635</v>
       </c>
       <c r="F14" t="n">
-        <v>1.677</v>
+        <v>1.6635</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.677</v>
+        <v>1.6635</v>
       </c>
       <c r="I14" t="n">
-        <v>1.81</v>
+        <v>1.8004</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.81</v>
+        <v>1.8004</v>
       </c>
       <c r="N14" t="n">
         <v>165</v>
@@ -1090,32 +1090,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6746</v>
+        <v>1.638</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7762</v>
+        <v>0.7593</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1381</v>
+        <v>0.1404</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6746</v>
+        <v>1.638</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6746</v>
+        <v>1.638</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6746</v>
+        <v>1.638</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8074</v>
+        <v>1.7728</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8074</v>
+        <v>1.7728</v>
       </c>
       <c r="N15" t="n">
         <v>165</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6532</v>
+        <v>1.5734</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7663</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1284</v>
+        <v>0.111</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6532</v>
+        <v>1.5734</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6532</v>
+        <v>1.5734</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6532</v>
+        <v>1.5734</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7843</v>
+        <v>1.703</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7843</v>
+        <v>1.703</v>
       </c>
       <c r="N16" t="n">
         <v>156</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.599</v>
+        <v>1.5297</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7412</v>
+        <v>0.7091</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1037</v>
+        <v>0.0911</v>
       </c>
       <c r="E17" t="n">
-        <v>1.599</v>
+        <v>1.5297</v>
       </c>
       <c r="F17" t="n">
-        <v>1.599</v>
+        <v>1.5297</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.599</v>
+        <v>1.5297</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7258</v>
+        <v>1.6556</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7258</v>
+        <v>1.6556</v>
       </c>
       <c r="N17" t="n">
         <v>165</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5106</v>
+        <v>1.4219</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7002</v>
+        <v>0.6591</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0635</v>
+        <v>0.042</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5106</v>
+        <v>1.4219</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5106</v>
+        <v>1.4219</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5106</v>
+        <v>1.4219</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6304</v>
+        <v>1.539</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6304</v>
+        <v>1.539</v>
       </c>
       <c r="N18" t="n">
         <v>156</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4484</v>
+        <v>1.3897</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6714</v>
+        <v>0.6442</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0351</v>
+        <v>0.0273</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4484</v>
+        <v>1.3897</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4484</v>
+        <v>1.3897</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4484</v>
+        <v>1.3897</v>
       </c>
       <c r="I19" t="n">
-        <v>1.524</v>
+        <v>1.465</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.524</v>
+        <v>1.465</v>
       </c>
       <c r="N19" t="n">
         <v>123</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3175</v>
+        <v>1.2192</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6107</v>
+        <v>0.5651</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0245</v>
+        <v>-0.0504</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3175</v>
+        <v>1.2192</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3175</v>
+        <v>1.2192</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3175</v>
+        <v>1.2192</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4962</v>
+        <v>1.391</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4962</v>
+        <v>1.391</v>
       </c>
       <c r="N20" t="n">
         <v>222</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1485</v>
+        <v>1.1784</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5324</v>
+        <v>0.5462</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1014</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1485</v>
+        <v>1.1784</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1485</v>
+        <v>1.1784</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1485</v>
+        <v>1.1784</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2396</v>
+        <v>1.2755</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2396</v>
+        <v>1.2755</v>
       </c>
       <c r="N21" t="n">
         <v>156</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9649</v>
+        <v>1.1081</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4473</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.185</v>
+        <v>-0.101</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9649</v>
+        <v>1.1081</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9649</v>
+        <v>1.1081</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9649</v>
+        <v>1.1081</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0153</v>
+        <v>1.3684</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0153</v>
+        <v>1.3684</v>
       </c>
       <c r="N22" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9512</v>
+        <v>1.0248</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4409</v>
+        <v>0.475</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1912</v>
+        <v>-0.1389</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9512</v>
+        <v>1.0248</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9512</v>
+        <v>1.0248</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9512</v>
+        <v>1.0248</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0266</v>
+        <v>1.1092</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0266</v>
+        <v>1.1092</v>
       </c>
       <c r="N23" t="n">
         <v>165</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.948</v>
+        <v>0.9443</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4394</v>
+        <v>0.4377</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1927</v>
+        <v>-0.1756</v>
       </c>
       <c r="E24" t="n">
-        <v>0.948</v>
+        <v>0.9443</v>
       </c>
       <c r="F24" t="n">
-        <v>0.948</v>
+        <v>0.9443</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.948</v>
+        <v>0.9443</v>
       </c>
       <c r="I24" t="n">
-        <v>1.162</v>
+        <v>0.9954</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.162</v>
+        <v>0.9954</v>
       </c>
       <c r="N24" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8848</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4101</v>
+        <v>0.4273</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2214</v>
+        <v>-0.1858</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8848</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8848</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8848</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.931</v>
+        <v>0.9718</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.931</v>
+        <v>0.9718</v>
       </c>
       <c r="N25" t="n">
         <v>123</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7639</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3591</v>
+        <v>0.3541</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2715</v>
+        <v>-0.2578</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7639</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7639</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7639</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7947</v>
+        <v>0.7843</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7947</v>
+        <v>0.7843</v>
       </c>
       <c r="N26" t="n">
         <v>87</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2628</v>
+        <v>0.2166</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3661</v>
+        <v>-0.393</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4672</v>
       </c>
       <c r="N27" t="n">
         <v>79</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1625</v>
+        <v>0.2227</v>
       </c>
       <c r="C28" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5502</v>
+        <v>-0.5043</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1625</v>
+        <v>0.2227</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1625</v>
+        <v>0.2227</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1625</v>
+        <v>0.2227</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1845</v>
+        <v>0.2541</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1845</v>
+        <v>0.2541</v>
       </c>
       <c r="N28" t="n">
         <v>222</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0425</v>
+        <v>0.0687</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0197</v>
+        <v>0.0318</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6049</v>
+        <v>-0.5745</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0425</v>
+        <v>0.0687</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0425</v>
+        <v>0.0687</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0425</v>
+        <v>0.0687</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0436</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0436</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>87</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0044</v>
+        <v>-0.0174</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6286</v>
+        <v>-0.6229</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0375</v>
       </c>
       <c r="N30" t="n">
         <v>79</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0459</v>
+        <v>-0.0499</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6693</v>
+        <v>-0.6548</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1076</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1043</v>
+        <v>-0.1134</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1043</v>
+        <v>-0.1134</v>
       </c>
       <c r="N31" t="n">
         <v>123</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1335</v>
+        <v>-0.1262</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0619</v>
+        <v>-0.0585</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.6633</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1335</v>
+        <v>-0.1262</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1335</v>
+        <v>-0.1262</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1335</v>
+        <v>-0.1262</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1335</v>
+        <v>-0.1262</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1335</v>
+        <v>-0.1262</v>
       </c>
       <c r="N32" t="n">
         <v>55</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hyper</t>
+          <t>Kairi</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3897</v>
+        <v>-0.4363</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1806</v>
+        <v>-0.2022</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8016</v>
+        <v>-0.8045</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3897</v>
+        <v>-0.4363</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3897</v>
+        <v>-0.4363</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3897</v>
+        <v>-0.4363</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3997</v>
+        <v>-0.4363</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3997</v>
+        <v>-0.4363</v>
       </c>
       <c r="N33" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kairi</t>
+          <t>Hyper</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4063</v>
+        <v>-0.4415</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1883</v>
+        <v>-0.2046</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8092</v>
+        <v>-0.8069</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4063</v>
+        <v>-0.4415</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4063</v>
+        <v>-0.4415</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4063</v>
+        <v>-0.4415</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4063</v>
+        <v>-0.4533</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4063</v>
+        <v>-0.4533</v>
       </c>
       <c r="N34" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.632</v>
+        <v>-0.6293</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2929</v>
+        <v>-0.2917</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9119</v>
+        <v>-0.8925</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.632</v>
+        <v>-0.6293</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.632</v>
+        <v>-0.6293</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.632</v>
+        <v>-0.6293</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6483</v>
+        <v>-0.6461</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6483</v>
+        <v>-0.6461</v>
       </c>
       <c r="N35" t="n">
         <v>87</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7371</v>
+        <v>-0.6834</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3417</v>
+        <v>-0.3168</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9597</v>
+        <v>-0.9171</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7371</v>
+        <v>-0.6834</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7371</v>
+        <v>-0.6834</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7371</v>
+        <v>-0.6834</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7371</v>
+        <v>-0.6834</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7371</v>
+        <v>-0.6834</v>
       </c>
       <c r="N36" t="n">
         <v>79</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0673</v>
+        <v>-1.0378</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4947</v>
+        <v>-0.481</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1101</v>
+        <v>-1.0786</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0673</v>
+        <v>-1.0378</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0673</v>
+        <v>-1.0378</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0673</v>
+        <v>-1.0378</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0673</v>
+        <v>-1.0378</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0673</v>
+        <v>-1.0378</v>
       </c>
       <c r="N37" t="n">
         <v>55</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>enanoks</t>
+          <t>TorPe</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1905</v>
+        <v>-1.1656</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5518</v>
+        <v>-0.5403</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1661</v>
+        <v>-1.1368</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1905</v>
+        <v>-1.1656</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1905</v>
+        <v>-1.1656</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1905</v>
+        <v>-1.1656</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.1905</v>
+        <v>-1.1656</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1905</v>
+        <v>-1.1656</v>
       </c>
       <c r="N38" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TorPe</t>
+          <t>enanoks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1952</v>
+        <v>-1.168</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.554</v>
+        <v>-0.5414</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1683</v>
+        <v>-1.1379</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1952</v>
+        <v>-1.168</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1952</v>
+        <v>-1.168</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1952</v>
+        <v>-1.168</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1952</v>
+        <v>-1.168</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1952</v>
+        <v>-1.168</v>
       </c>
       <c r="N39" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3425</v>
+        <v>-1.3383</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6223</v>
+        <v>-0.6203</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2353</v>
+        <v>-1.2154</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3425</v>
+        <v>-1.3383</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3425</v>
+        <v>-1.3383</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3425</v>
+        <v>-1.3383</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3425</v>
+        <v>-1.3383</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3425</v>
+        <v>-1.3383</v>
       </c>
       <c r="N40" t="n">
         <v>55</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8833</v>
+        <v>-1.9377</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.873</v>
+        <v>-0.8982</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4815</v>
+        <v>-1.4885</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8833</v>
+        <v>-1.9377</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8833</v>
+        <v>-1.9377</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8833</v>
+        <v>-1.9377</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8833</v>
+        <v>-1.9377</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8833</v>
+        <v>-1.9377</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2429,10 +2429,10 @@
         <v>1.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2159</v>
+        <v>0.1728</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2611</v>
+        <v>5.0112</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.03</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1027</v>
+        <v>0.0756</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9783</v>
+        <v>2.1924</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0711</v>
+        <v>-0.0574</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.0619</v>
+        <v>-1.6646</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.0694</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.4534</v>
+        <v>-2.0126</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1675</v>
+        <v>-0.1474</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.8575</v>
+        <v>-4.2746</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1695</v>
+        <v>1.184</v>
       </c>
       <c r="J7" t="n">
-        <v>33.9155</v>
+        <v>34.336</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.4</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9597</v>
+        <v>0.9495</v>
       </c>
       <c r="J8" t="n">
-        <v>27.8313</v>
+        <v>27.5355</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0257</v>
+        <v>-0.0203</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7453</v>
+        <v>-0.5887</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1975</v>
+        <v>-0.1628</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.7275</v>
+        <v>-4.7212</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4245</v>
+        <v>-0.3826</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.3105</v>
+        <v>-11.0954</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.48</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8777</v>
+        <v>0.833</v>
       </c>
       <c r="J12" t="n">
-        <v>26.331</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1278</v>
+        <v>0.0964</v>
       </c>
       <c r="J13" t="n">
-        <v>3.834</v>
+        <v>2.892</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.96</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0573</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.13</v>
+        <v>-1.719</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2894</v>
+        <v>-0.2708</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.682</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.65</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3911</v>
+        <v>-0.3798</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.733</v>
+        <v>-11.394</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7659</v>
+        <v>0.7366</v>
       </c>
       <c r="J17" t="n">
-        <v>22.977</v>
+        <v>22.098</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4768</v>
+        <v>0.4355</v>
       </c>
       <c r="J18" t="n">
-        <v>14.304</v>
+        <v>13.065</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1273</v>
+        <v>0.1033</v>
       </c>
       <c r="J19" t="n">
-        <v>3.819</v>
+        <v>3.099</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3002</v>
+        <v>-0.259</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.006</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3002</v>
+        <v>-0.259</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.006</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2143</v>
+        <v>1.2299</v>
       </c>
       <c r="J22" t="n">
-        <v>29.1432</v>
+        <v>29.5176</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0106</v>
+        <v>1.0122</v>
       </c>
       <c r="J23" t="n">
-        <v>24.2544</v>
+        <v>24.2928</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.35</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8324</v>
+        <v>0.8155</v>
       </c>
       <c r="J24" t="n">
-        <v>19.9776</v>
+        <v>19.572</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.32</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7756</v>
+        <v>0.7556</v>
       </c>
       <c r="J25" t="n">
-        <v>18.6144</v>
+        <v>18.1344</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4769</v>
+        <v>-0.4401</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.4456</v>
+        <v>-10.5624</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.24</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5913</v>
+        <v>0.5513</v>
       </c>
       <c r="J27" t="n">
-        <v>14.1912</v>
+        <v>13.2312</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.79</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2411</v>
+        <v>-0.2248</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.7864</v>
+        <v>-5.3952</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.78</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2506</v>
+        <v>-0.2342</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.0144</v>
+        <v>-5.6208</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.458</v>
+        <v>-0.4518</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.992</v>
+        <v>-10.8432</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5363</v>
+        <v>-0.54</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.8712</v>
+        <v>-12.96</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.65</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2757</v>
+        <v>1.2939</v>
       </c>
       <c r="J32" t="n">
-        <v>29.3411</v>
+        <v>29.7597</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.56</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1593</v>
+        <v>1.1735</v>
       </c>
       <c r="J33" t="n">
-        <v>26.6639</v>
+        <v>26.9905</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.26</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6553</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>15.0719</v>
+        <v>14.5015</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.24</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6137</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>14.1151</v>
+        <v>13.5056</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.96</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2276</v>
+        <v>-0.1958</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.2348</v>
+        <v>-4.5034</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.99</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0159</v>
+        <v>0.0255</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3657</v>
+        <v>0.5865</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.229</v>
+        <v>-0.2133</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.267</v>
+        <v>-4.9059</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.68</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3395</v>
+        <v>-0.3249</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.8085</v>
+        <v>-7.4727</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3756</v>
+        <v>-0.3626</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.6388</v>
+        <v>-8.3398</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4024</v>
+        <v>-0.3912</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.2552</v>
+        <v>-8.9976</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.09</v>
       </c>
       <c r="I42" t="n">
-        <v>0.236</v>
+        <v>0.1908</v>
       </c>
       <c r="J42" t="n">
-        <v>6.608</v>
+        <v>5.3424</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0453</v>
+        <v>0.0304</v>
       </c>
       <c r="J43" t="n">
-        <v>1.2684</v>
+        <v>0.8512</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.99</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0245</v>
+        <v>-0.0178</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.4984</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1101</v>
+        <v>-0.0927</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.0828</v>
+        <v>-2.5956</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1567</v>
+        <v>-0.1368</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.3876</v>
+        <v>-3.8304</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.97</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7149</v>
+        <v>1.7751</v>
       </c>
       <c r="J47" t="n">
-        <v>48.0172</v>
+        <v>49.7028</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8339</v>
+        <v>0.8117</v>
       </c>
       <c r="J48" t="n">
-        <v>23.3492</v>
+        <v>22.7276</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.07</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2293</v>
+        <v>0.1996</v>
       </c>
       <c r="J49" t="n">
-        <v>6.4204</v>
+        <v>5.5888</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.82</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5783</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-16.1924</v>
+        <v>-15.1704</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.78</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6701</v>
+        <v>-0.6391</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.7628</v>
+        <v>-17.8948</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.31</v>
       </c>
       <c r="I52" t="n">
-        <v>0.769</v>
+        <v>0.7436</v>
       </c>
       <c r="J52" t="n">
-        <v>20.763</v>
+        <v>20.0772</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.3</v>
       </c>
       <c r="I53" t="n">
-        <v>0.749</v>
+        <v>0.7225</v>
       </c>
       <c r="J53" t="n">
-        <v>20.223</v>
+        <v>19.5075</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.27</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6883</v>
+        <v>0.6591</v>
       </c>
       <c r="J54" t="n">
-        <v>18.5841</v>
+        <v>17.7957</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.16</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4537</v>
+        <v>0.42</v>
       </c>
       <c r="J55" t="n">
-        <v>12.2499</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.07</v>
       </c>
       <c r="I56" t="n">
-        <v>0.225</v>
+        <v>0.1956</v>
       </c>
       <c r="J56" t="n">
-        <v>6.075</v>
+        <v>5.2812</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.06</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1998</v>
+        <v>0.1596</v>
       </c>
       <c r="J57" t="n">
-        <v>5.3946</v>
+        <v>4.3092</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0614</v>
+        <v>-0.0505</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.6578</v>
+        <v>-1.3635</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2297</v>
+        <v>-0.2105</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.2019</v>
+        <v>-5.6835</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2782</v>
+        <v>-0.2596</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.5114</v>
+        <v>-7.0092</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.73</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3066</v>
+        <v>-0.289</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.2782</v>
+        <v>-7.803</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.63</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2421</v>
+        <v>1.2594</v>
       </c>
       <c r="J62" t="n">
-        <v>28.5683</v>
+        <v>28.9662</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.48</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0463</v>
+        <v>1.0553</v>
       </c>
       <c r="J63" t="n">
-        <v>24.0649</v>
+        <v>24.2719</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.48</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0463</v>
+        <v>1.0553</v>
       </c>
       <c r="J64" t="n">
-        <v>24.0649</v>
+        <v>24.2719</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.31</v>
       </c>
       <c r="I65" t="n">
-        <v>0.7498</v>
+        <v>0.7313</v>
       </c>
       <c r="J65" t="n">
-        <v>17.2454</v>
+        <v>16.8199</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.063</v>
+        <v>-0.0601</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.449</v>
+        <v>-1.3823</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.31</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7553</v>
+        <v>0.7413</v>
       </c>
       <c r="J67" t="n">
-        <v>17.3719</v>
+        <v>17.0499</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2626</v>
+        <v>-0.2483</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.0398</v>
+        <v>-5.7109</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.62</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3883</v>
+        <v>-0.3767</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.930899999999999</v>
+        <v>-8.664099999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.46</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5292</v>
+        <v>-0.5312</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.1716</v>
+        <v>-12.2176</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.36</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6158</v>
+        <v>-0.6313</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.1634</v>
+        <v>-14.5199</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.17</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4202</v>
+        <v>0.367</v>
       </c>
       <c r="J72" t="n">
-        <v>12.1858</v>
+        <v>10.643</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.1837</v>
+        <v>-1.8299</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0886</v>
+        <v>-0.0752</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.5694</v>
+        <v>-2.1808</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.66</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3711</v>
+        <v>-0.3573</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.7619</v>
+        <v>-10.3617</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.6</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4248</v>
+        <v>-0.4158</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.3192</v>
+        <v>-12.0582</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.57</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1916</v>
+        <v>1.2061</v>
       </c>
       <c r="J77" t="n">
-        <v>34.5564</v>
+        <v>34.9769</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.19</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5198</v>
+        <v>0.4871</v>
       </c>
       <c r="J78" t="n">
-        <v>15.0742</v>
+        <v>14.1259</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.19</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5198</v>
+        <v>0.4871</v>
       </c>
       <c r="J79" t="n">
-        <v>15.0742</v>
+        <v>14.1259</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.17</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4749</v>
+        <v>0.4418</v>
       </c>
       <c r="J80" t="n">
-        <v>13.7721</v>
+        <v>12.8122</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>1.05</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1637</v>
+        <v>0.1378</v>
       </c>
       <c r="J81" t="n">
-        <v>4.7473</v>
+        <v>3.9962</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.78</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4281</v>
+        <v>1.4547</v>
       </c>
       <c r="J82" t="n">
-        <v>29.9901</v>
+        <v>30.5487</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.62</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2281</v>
+        <v>1.245</v>
       </c>
       <c r="J83" t="n">
-        <v>25.7901</v>
+        <v>26.145</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.4</v>
       </c>
       <c r="I84" t="n">
-        <v>0.9173</v>
+        <v>0.9099</v>
       </c>
       <c r="J84" t="n">
-        <v>19.2633</v>
+        <v>19.1079</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.09</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2535</v>
+        <v>0.222</v>
       </c>
       <c r="J85" t="n">
-        <v>5.3235</v>
+        <v>4.662</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>1.05</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1388</v>
+        <v>0.1115</v>
       </c>
       <c r="J86" t="n">
-        <v>2.9148</v>
+        <v>2.3415</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.23</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5859</v>
+        <v>0.5494</v>
       </c>
       <c r="J87" t="n">
-        <v>12.3039</v>
+        <v>11.5374</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0407</v>
+        <v>-0.0287</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.8547</v>
+        <v>-0.6027</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.6</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.4111</v>
+        <v>-0.4006</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.633100000000001</v>
+        <v>-8.412599999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.53</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4729</v>
+        <v>-0.4683</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.930899999999999</v>
+        <v>-9.834300000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5941</v>
+        <v>-0.6065</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.4761</v>
+        <v>-12.7365</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.01</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0639</v>
+        <v>0.045</v>
       </c>
       <c r="J92" t="n">
-        <v>1.5975</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0148</v>
+        <v>-0.0103</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.37</v>
+        <v>-0.2575</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.97</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0487</v>
+        <v>-0.0391</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.2175</v>
+        <v>-0.9775</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2988</v>
+        <v>-0.2808</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.47</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3454</v>
+        <v>-0.3298</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.635</v>
+        <v>-8.244999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.68</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3276</v>
+        <v>1.3486</v>
       </c>
       <c r="J97" t="n">
-        <v>33.19</v>
+        <v>33.715</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.64</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2759</v>
+        <v>1.2941</v>
       </c>
       <c r="J98" t="n">
-        <v>31.8975</v>
+        <v>32.3525</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0922</v>
+        <v>0.0716</v>
       </c>
       <c r="J99" t="n">
-        <v>2.305</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.02</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0557</v>
+        <v>0.0393</v>
       </c>
       <c r="J100" t="n">
-        <v>1.3925</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.98</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1469</v>
+        <v>-0.1205</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.6725</v>
+        <v>-3.0125</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.19</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5451</v>
+        <v>0.5051</v>
       </c>
       <c r="J102" t="n">
-        <v>19.6236</v>
+        <v>18.1836</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5451</v>
+        <v>0.5051</v>
       </c>
       <c r="J103" t="n">
-        <v>19.6236</v>
+        <v>18.1836</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.13</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4033</v>
+        <v>0.3626</v>
       </c>
       <c r="J104" t="n">
-        <v>14.5188</v>
+        <v>13.0536</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1815</v>
+        <v>-0.1475</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.534</v>
+        <v>-5.31</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.88</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4081</v>
+        <v>-0.3651</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.6916</v>
+        <v>-13.1436</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.34</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6449</v>
+        <v>0.5857</v>
       </c>
       <c r="J107" t="n">
-        <v>23.2164</v>
+        <v>21.0852</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3883</v>
+        <v>0.333</v>
       </c>
       <c r="J108" t="n">
-        <v>13.9788</v>
+        <v>11.988</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.03</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0951</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>3.4236</v>
+        <v>2.574</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.174</v>
+        <v>-0.1535</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.264</v>
+        <v>-5.526</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.84</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2167</v>
+        <v>-0.1962</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.8012</v>
+        <v>-7.0632</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.69</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3555</v>
+        <v>1.3794</v>
       </c>
       <c r="J112" t="n">
-        <v>33.8875</v>
+        <v>34.485</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.27</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6901</v>
+        <v>0.6604</v>
       </c>
       <c r="J113" t="n">
-        <v>17.2525</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.227</v>
+        <v>0.1974</v>
       </c>
       <c r="J114" t="n">
-        <v>5.675</v>
+        <v>4.935</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.198</v>
+        <v>0.17</v>
       </c>
       <c r="J115" t="n">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.96</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2071</v>
+        <v>-0.1729</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.1775</v>
+        <v>-4.3225</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3399</v>
+        <v>0.2885</v>
       </c>
       <c r="J117" t="n">
-        <v>8.4975</v>
+        <v>7.2125</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2391</v>
+        <v>0.1946</v>
       </c>
       <c r="J118" t="n">
-        <v>5.9775</v>
+        <v>4.865</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.02</v>
       </c>
       <c r="I119" t="n">
-        <v>0.095</v>
+        <v>0.0696</v>
       </c>
       <c r="J119" t="n">
-        <v>2.375</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.75</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2893</v>
+        <v>-0.271</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.2325</v>
+        <v>-6.775</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.42</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.581</v>
+        <v>-0.5933</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.525</v>
+        <v>-14.8325</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.88</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5215</v>
+        <v>1.555</v>
       </c>
       <c r="J122" t="n">
-        <v>30.43</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.58</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1598</v>
+        <v>1.1794</v>
       </c>
       <c r="J123" t="n">
-        <v>23.196</v>
+        <v>23.588</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.53</v>
       </c>
       <c r="I124" t="n">
-        <v>1.0984</v>
+        <v>1.1173</v>
       </c>
       <c r="J124" t="n">
-        <v>21.968</v>
+        <v>22.346</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.47</v>
       </c>
       <c r="I125" t="n">
-        <v>1.0183</v>
+        <v>1.0302</v>
       </c>
       <c r="J125" t="n">
-        <v>20.366</v>
+        <v>20.604</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>1.23</v>
       </c>
       <c r="I126" t="n">
-        <v>0.5632</v>
+        <v>0.5371</v>
       </c>
       <c r="J126" t="n">
-        <v>11.264</v>
+        <v>10.742</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>0.8</v>
       </c>
       <c r="I127" t="n">
-        <v>-0.2152</v>
+        <v>-0.2002</v>
       </c>
       <c r="J127" t="n">
-        <v>-4.304</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2461</v>
+        <v>-0.2321</v>
       </c>
       <c r="J128" t="n">
-        <v>-4.922</v>
+        <v>-4.642</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.7</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3137</v>
+        <v>-0.3015</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.274</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.6</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4009</v>
+        <v>-0.3909</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.018000000000001</v>
+        <v>-7.818</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.44</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5416</v>
+        <v>-0.545</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.832</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.72</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3318</v>
+        <v>1.3552</v>
       </c>
       <c r="J132" t="n">
-        <v>25.3042</v>
+        <v>25.7488</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.66</v>
       </c>
       <c r="I133" t="n">
-        <v>1.2588</v>
+        <v>1.2799</v>
       </c>
       <c r="J133" t="n">
-        <v>23.9172</v>
+        <v>24.3181</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.48</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0333</v>
+        <v>1.0468</v>
       </c>
       <c r="J134" t="n">
-        <v>19.6327</v>
+        <v>19.8892</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.46</v>
       </c>
       <c r="I135" t="n">
-        <v>1.0038</v>
+        <v>1.0136</v>
       </c>
       <c r="J135" t="n">
-        <v>19.0722</v>
+        <v>19.2584</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.34</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7881</v>
+        <v>0.7765</v>
       </c>
       <c r="J136" t="n">
-        <v>14.9739</v>
+        <v>14.7535</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>0.79</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.2151</v>
+        <v>-0.1993</v>
       </c>
       <c r="J137" t="n">
-        <v>-4.0869</v>
+        <v>-3.7867</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.75</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2568</v>
+        <v>-0.2433</v>
       </c>
       <c r="J138" t="n">
-        <v>-4.8792</v>
+        <v>-4.6227</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.55</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4386</v>
+        <v>-0.4317</v>
       </c>
       <c r="J139" t="n">
-        <v>-8.333399999999999</v>
+        <v>-8.202299999999999</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.54</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4473</v>
+        <v>-0.441</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.498699999999999</v>
+        <v>-8.379</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.45</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5265</v>
+        <v>-0.5276</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.0035</v>
+        <v>-10.0244</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.75</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4331</v>
+        <v>1.4629</v>
       </c>
       <c r="J142" t="n">
-        <v>41.5599</v>
+        <v>42.4241</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.3</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7511</v>
+        <v>0.7242</v>
       </c>
       <c r="J143" t="n">
-        <v>21.7819</v>
+        <v>21.0018</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4321</v>
+        <v>0.3979</v>
       </c>
       <c r="J144" t="n">
-        <v>12.5309</v>
+        <v>11.5391</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.03</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1024</v>
+        <v>0.082</v>
       </c>
       <c r="J145" t="n">
-        <v>2.9696</v>
+        <v>2.378</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.82</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5806</v>
+        <v>-0.5446</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.8374</v>
+        <v>-15.7934</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.22</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4887</v>
+        <v>0.4317</v>
       </c>
       <c r="J147" t="n">
-        <v>14.1723</v>
+        <v>12.5193</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.16</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3829</v>
+        <v>0.3282</v>
       </c>
       <c r="J148" t="n">
-        <v>11.1041</v>
+        <v>9.517799999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2353</v>
+        <v>-0.2153</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.8237</v>
+        <v>-6.2437</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.74</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3032</v>
+        <v>-0.2853</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.7928</v>
+        <v>-8.2737</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3498</v>
+        <v>-0.3347</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.1442</v>
+        <v>-9.706300000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>2.33</v>
       </c>
       <c r="I152" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J152" t="n">
-        <v>34.8696</v>
+        <v>35.6724</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.64</v>
       </c>
       <c r="I153" t="n">
-        <v>1.231</v>
+        <v>1.2525</v>
       </c>
       <c r="J153" t="n">
-        <v>22.158</v>
+        <v>22.545</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.54</v>
       </c>
       <c r="I154" t="n">
-        <v>1.1092</v>
+        <v>1.1292</v>
       </c>
       <c r="J154" t="n">
-        <v>19.9656</v>
+        <v>20.3256</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.25</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6018</v>
+        <v>0.5779</v>
       </c>
       <c r="J155" t="n">
-        <v>10.8324</v>
+        <v>10.4022</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.07</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1731</v>
+        <v>0.1391</v>
       </c>
       <c r="J156" t="n">
-        <v>3.1158</v>
+        <v>2.5038</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.1</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4052</v>
+        <v>0.3896</v>
       </c>
       <c r="J157" t="n">
-        <v>7.2936</v>
+        <v>7.0128</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.68</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3269</v>
+        <v>-0.3162</v>
       </c>
       <c r="J158" t="n">
-        <v>-5.8842</v>
+        <v>-5.6916</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.62</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3795</v>
+        <v>-0.37</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.831</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.53</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4575</v>
+        <v>-0.4518</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.234999999999999</v>
+        <v>-8.132400000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.2</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7467</v>
+        <v>-0.7879</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.4406</v>
+        <v>-14.1822</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.09</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2466</v>
+        <v>0.2003</v>
       </c>
       <c r="J162" t="n">
-        <v>7.1514</v>
+        <v>5.8087</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1827</v>
+        <v>0.1432</v>
       </c>
       <c r="J163" t="n">
-        <v>5.2983</v>
+        <v>4.1528</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.98</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0384</v>
+        <v>-0.03</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.1136</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.85</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1953</v>
+        <v>-0.1752</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.6637</v>
+        <v>-5.0808</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.68</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3597</v>
+        <v>-0.3454</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.4313</v>
+        <v>-10.0166</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.44</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0367</v>
+        <v>1.0402</v>
       </c>
       <c r="J167" t="n">
-        <v>30.0643</v>
+        <v>30.1658</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.26</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6871</v>
+        <v>0.6538</v>
       </c>
       <c r="J168" t="n">
-        <v>19.9259</v>
+        <v>18.9602</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5345</v>
+        <v>0.4961</v>
       </c>
       <c r="J169" t="n">
-        <v>15.5005</v>
+        <v>14.3869</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2532</v>
+        <v>-0.2143</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.3428</v>
+        <v>-6.2147</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.77</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6793</v>
+        <v>-0.647</v>
       </c>
       <c r="J171" t="n">
-        <v>-19.6997</v>
+        <v>-18.763</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.92</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0737</v>
+        <v>-0.055</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.6951</v>
+        <v>-1.265</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.66</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3484</v>
+        <v>-0.337</v>
       </c>
       <c r="J173" t="n">
-        <v>-8.013199999999999</v>
+        <v>-7.751</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.64</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3651</v>
+        <v>-0.3541</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.3973</v>
+        <v>-8.144299999999999</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.55</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4439</v>
+        <v>-0.4367</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.2097</v>
+        <v>-10.0441</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4879</v>
+        <v>-0.4847</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.2217</v>
+        <v>-11.1481</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.87</v>
       </c>
       <c r="I177" t="n">
-        <v>1.529</v>
+        <v>1.5626</v>
       </c>
       <c r="J177" t="n">
-        <v>35.167</v>
+        <v>35.9398</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.61</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2092</v>
+        <v>1.2265</v>
       </c>
       <c r="J178" t="n">
-        <v>27.8116</v>
+        <v>28.2095</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.46</v>
       </c>
       <c r="I179" t="n">
-        <v>1.0118</v>
+        <v>1.0183</v>
       </c>
       <c r="J179" t="n">
-        <v>23.2714</v>
+        <v>23.4209</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.27</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6624</v>
+        <v>0.6407</v>
       </c>
       <c r="J180" t="n">
-        <v>15.2352</v>
+        <v>14.7361</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3041</v>
+        <v>-0.2717</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.9943</v>
+        <v>-6.2491</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.83</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4553</v>
+        <v>1.4856</v>
       </c>
       <c r="J182" t="n">
-        <v>26.1954</v>
+        <v>26.7408</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.81</v>
       </c>
       <c r="I183" t="n">
-        <v>1.4318</v>
+        <v>1.4609</v>
       </c>
       <c r="J183" t="n">
-        <v>25.7724</v>
+        <v>26.2962</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.48</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0279</v>
+        <v>1.0427</v>
       </c>
       <c r="J184" t="n">
-        <v>18.5022</v>
+        <v>18.7686</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.42</v>
       </c>
       <c r="I185" t="n">
-        <v>0.931</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>16.758</v>
+        <v>16.794</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.41</v>
       </c>
       <c r="I186" t="n">
-        <v>0.913</v>
+        <v>0.9129</v>
       </c>
       <c r="J186" t="n">
-        <v>16.434</v>
+        <v>16.4322</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2931</v>
+        <v>-0.2806</v>
       </c>
       <c r="J187" t="n">
-        <v>-5.2758</v>
+        <v>-5.0508</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.66</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3236</v>
+        <v>-0.3138</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.8248</v>
+        <v>-5.6484</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.61</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3724</v>
+        <v>-0.3663</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.7032</v>
+        <v>-6.5934</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.34</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6101</v>
+        <v>-0.6222</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.9818</v>
+        <v>-11.1996</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.32</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6282</v>
+        <v>-0.6432</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.3076</v>
+        <v>-11.5776</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.55</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1843</v>
+        <v>1.1994</v>
       </c>
       <c r="J192" t="n">
-        <v>35.529</v>
+        <v>35.982</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4163</v>
+        <v>0.3795</v>
       </c>
       <c r="J193" t="n">
-        <v>12.489</v>
+        <v>11.385</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.09</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2915</v>
+        <v>0.2581</v>
       </c>
       <c r="J194" t="n">
-        <v>8.744999999999999</v>
+        <v>7.743</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.07</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2367</v>
+        <v>0.2058</v>
       </c>
       <c r="J195" t="n">
-        <v>7.101</v>
+        <v>6.174</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.91</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3445</v>
+        <v>-0.3029</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.335</v>
+        <v>-9.087</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.17</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3993</v>
+        <v>0.3438</v>
       </c>
       <c r="J197" t="n">
-        <v>11.979</v>
+        <v>10.314</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.14</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3444</v>
+        <v>0.2913</v>
       </c>
       <c r="J198" t="n">
-        <v>10.332</v>
+        <v>8.739000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.86</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1846</v>
+        <v>-0.1647</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.538</v>
+        <v>-4.941</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.79</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2557</v>
+        <v>-0.236</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.671</v>
+        <v>-7.08</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3504</v>
+        <v>-0.3353</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.512</v>
+        <v>-10.059</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.24</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6671</v>
+        <v>0.6315</v>
       </c>
       <c r="J202" t="n">
-        <v>24.0156</v>
+        <v>22.734</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5543</v>
+        <v>0.5138</v>
       </c>
       <c r="J203" t="n">
-        <v>19.9548</v>
+        <v>18.4968</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3343</v>
+        <v>0.2937</v>
       </c>
       <c r="J204" t="n">
-        <v>12.0348</v>
+        <v>10.5732</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2065</v>
+        <v>-0.1708</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.434</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-30.1392</v>
+        <v>-29.376</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.3</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5848</v>
+        <v>0.525</v>
       </c>
       <c r="J207" t="n">
-        <v>21.0528</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.27</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5376</v>
+        <v>0.4779</v>
       </c>
       <c r="J208" t="n">
-        <v>19.3536</v>
+        <v>17.2044</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.04</v>
       </c>
       <c r="I209" t="n">
-        <v>0.12</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>4.32</v>
+        <v>3.3048</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.85</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2057</v>
+        <v>-0.1851</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.4052</v>
+        <v>-6.6636</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.78</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2763</v>
+        <v>-0.2575</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.9468</v>
+        <v>-9.27</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.65</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2968</v>
+        <v>1.3164</v>
       </c>
       <c r="J212" t="n">
-        <v>33.7168</v>
+        <v>34.2264</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.45</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0252</v>
+        <v>1.0271</v>
       </c>
       <c r="J213" t="n">
-        <v>26.6552</v>
+        <v>26.7046</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.26</v>
       </c>
       <c r="I214" t="n">
-        <v>0.666</v>
+        <v>0.6368</v>
       </c>
       <c r="J214" t="n">
-        <v>17.316</v>
+        <v>16.5568</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3802</v>
+        <v>0.347</v>
       </c>
       <c r="J215" t="n">
-        <v>9.885199999999999</v>
+        <v>9.022</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8714</v>
+        <v>-0.8593</v>
       </c>
       <c r="J216" t="n">
-        <v>-22.6564</v>
+        <v>-22.3418</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.08</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2456</v>
+        <v>0.2013</v>
       </c>
       <c r="J217" t="n">
-        <v>6.3856</v>
+        <v>5.2338</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.88</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1584</v>
+        <v>-0.1411</v>
       </c>
       <c r="J218" t="n">
-        <v>-4.1184</v>
+        <v>-3.6686</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.85</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1892</v>
+        <v>-0.1709</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.9192</v>
+        <v>-4.4434</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.85</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1892</v>
+        <v>-0.1709</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.9192</v>
+        <v>-4.4434</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3975</v>
+        <v>-0.3859</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.335</v>
+        <v>-10.0334</v>
       </c>
     </row>
   </sheetData>
